--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>תשלום עבור חשבונית (כמו 13/07 ו-16/08 - 16,520 כל אחד; ברשימת הממתינים נרשם 16,250). משותפת - חצי מטה</t>
+          <t>תשלום עבור חשבונית (כמו 13/07 ו-16/08 - 16,520 כל אחד; ברשימת הממתינים נרשם 16,250). משותפת - חצי מטה · ✅ אושר ע"י שמואל 14/10</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="D22" s="105" t="inlineStr">
         <is>
-          <t>✅ שולם 13/10/2026 בצ׳ק 5000289 - 16,520 ₪ (כאן נרשם 16,250; גם התשלומים ב-13/07 וב-16/08 היו 16,520)</t>
+          <t>✅ שולם 13/10/2026 בצ׳ק 5000289 - 16,520 ₪ (כאן נרשם 16,250; גם התשלומים ב-13/07 וב-16/08 היו 16,520) · ✅ אושר ע"י שמואל 14/10</t>
         </is>
       </c>
       <c r="E22" s="106" t="n"/>

--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -16352,7 +16352,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>על חשבון חשבון עסקה 40117 (15,904) - נותרו 163 ₪ (לבדוק: ניכוי במקור?)</t>
+          <t>חשבון עסקה 40117 - עובדים ספטמבר. ✅ שולם במלואו (הסכום הנכון לפי שמואל 14/10)</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -18592,11 +18592,11 @@
         </is>
       </c>
       <c r="C40" s="111" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="D40" s="112" t="inlineStr">
         <is>
-          <t>✅ התקבלו 15,741 ₪ ב-12/10/2026 (העברה מאלי שי בן-חיים) - נותרו 163 ₪ (לבדוק: ניכוי במקור / הפרש)</t>
+          <t>✅ שולם במלואו 12/10/2026 - 15,741 ₪ (העברה מאלי שי בן-חיים). הסכום הנכון לפי שמואל 14/10</t>
         </is>
       </c>
       <c r="E40" s="109" t="n"/>

--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -954,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="131" min="1" max="2"/>
@@ -1941,119 +1941,125 @@
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="131">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>01/002772</t>
+        </is>
+      </c>
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="n">
+        <v>301259.9</v>
+      </c>
+      <c r="E40" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="39">
+        <f>D40-E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>⏳ חשבונית מס 01/002772 מ-13/10/2026 · 255,305 + מע"מ 45,954.90 · אספקת כ"א 09.26 לאתרים שונים בירושלים · מועד תשלום טרם נקבע</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" s="131">
+      <c r="A41" s="43" t="inlineStr">
         <is>
           <t>סה״כ</t>
         </is>
       </c>
-      <c r="B40" s="44" t="n"/>
-      <c r="C40" s="44" t="n"/>
-      <c r="D40" s="45">
-        <f>SUM(D32:D39)</f>
-        <v/>
-      </c>
-      <c r="E40" s="45">
-        <f>SUM(E32:E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="45">
-        <f>SUM(F32:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="44" t="n"/>
-    </row>
-    <row r="41" ht="14.25" customHeight="1" s="131"/>
-    <row r="42" ht="14.25" customHeight="1" s="131">
-      <c r="A42" s="72" t="inlineStr">
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="45">
+        <f>SUM(D32:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="45">
+        <f>SUM(E32:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="45">
+        <f>SUM(F32:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="44" t="n"/>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" s="131"/>
+    <row r="43" ht="14.25" customHeight="1" s="131">
+      <c r="A43" s="72" t="inlineStr">
         <is>
           <t>פסגת ליאם כח אדם בע"מ</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1" s="131">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="14.25" customHeight="1" s="131">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1" s="131">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>50116</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="n">
-        <v>17098.2</v>
-      </c>
-      <c r="E44" s="24" t="n">
-        <v>17098.2</v>
-      </c>
-      <c r="F44" s="29">
-        <f>D44-E44</f>
-        <v/>
-      </c>
-      <c r="G44" s="30" t="inlineStr">
-        <is>
-          <t>05/08/2026 ✅</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="131">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="59" t="n">
-        <v>46121</v>
+          <t>יולי</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>50116</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
       </c>
       <c r="D45" s="23" t="n">
-        <v>37541.7</v>
+        <v>17098.2</v>
       </c>
       <c r="E45" s="24" t="n">
-        <v>37541.7</v>
+        <v>17098.2</v>
       </c>
       <c r="F45" s="29">
         <f>D45-E45</f>
@@ -2061,25 +2067,25 @@
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>04/09 ✅ שולם במלואו</t>
+          <t>05/08/2026 ✅</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="131">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>50156</v>
-      </c>
-      <c r="C46" s="59" t="n"/>
+          <t>אוגוסט</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="59" t="n">
+        <v>46121</v>
+      </c>
       <c r="D46" s="23" t="n">
-        <v>12685.71</v>
+        <v>37541.7</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>12685.71</v>
+        <v>37541.7</v>
       </c>
       <c r="F46" s="29">
         <f>D46-E46</f>
@@ -2087,388 +2093,384 @@
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
+          <t>04/09 ✅ שולם במלואו</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1" s="131">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>50156</v>
+      </c>
+      <c r="C47" s="59" t="n"/>
+      <c r="D47" s="23" t="n">
+        <v>12685.71</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <v>12685.71</v>
+      </c>
+      <c r="F47" s="29">
+        <f>D47-E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="30" t="inlineStr">
+        <is>
           <t>06/10 ✅ שולם במלואו (חן 50156)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1" s="131">
-      <c r="A47" s="43" t="inlineStr">
+    <row r="48" ht="14.25" customHeight="1" s="131">
+      <c r="A48" s="43" t="inlineStr">
         <is>
           <t>סה״כ</t>
         </is>
       </c>
-      <c r="B47" s="44" t="n"/>
-      <c r="C47" s="44" t="n"/>
-      <c r="D47" s="45">
-        <f>SUM(D44:D46)</f>
-        <v/>
-      </c>
-      <c r="E47" s="45">
-        <f>SUM(E44:E46)</f>
-        <v/>
-      </c>
-      <c r="F47" s="45">
-        <f>SUM(F44:F46)</f>
-        <v/>
-      </c>
-      <c r="G47" s="44" t="n"/>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="131">
-      <c r="A48" s="43" t="n"/>
       <c r="B48" s="44" t="n"/>
       <c r="C48" s="44" t="n"/>
-      <c r="D48" s="45" t="n"/>
-      <c r="E48" s="45" t="n"/>
-      <c r="F48" s="45" t="n"/>
+      <c r="D48" s="45">
+        <f>SUM(D45:D47)</f>
+        <v/>
+      </c>
+      <c r="E48" s="45">
+        <f>SUM(E45:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="45">
+        <f>SUM(F45:F47)</f>
+        <v/>
+      </c>
       <c r="G48" s="44" t="n"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="131">
-      <c r="A49" s="72" t="inlineStr">
+      <c r="A49" s="43" t="n"/>
+      <c r="B49" s="44" t="n"/>
+      <c r="C49" s="44" t="n"/>
+      <c r="D49" s="45" t="n"/>
+      <c r="E49" s="45" t="n"/>
+      <c r="F49" s="45" t="n"/>
+      <c r="G49" s="44" t="n"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" s="131">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>עוצמת התמרון בע"מ   |   מועד תשלום: ה-15 לחודש</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1" s="131">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51" ht="14.25" customHeight="1" s="131">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1" s="131">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="52" ht="14.25" customHeight="1" s="131">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>יולי</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>SI266000108</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="D51" s="23" t="n">
+      <c r="D52" s="23" t="n">
         <v>10377.51</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E52" s="24" t="n">
         <v>10113.67</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F52" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="30" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>17/08 ✅ - שולם בניכוי 3%</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1" s="131">
-      <c r="A52" s="43" t="inlineStr">
+    <row r="53" ht="14.25" customHeight="1" s="131">
+      <c r="A53" s="43" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B52" s="44" t="n"/>
-      <c r="C52" s="44" t="n"/>
-      <c r="D52" s="45" t="n">
-        <v>10377.51</v>
-      </c>
-      <c r="E52" s="45" t="n">
-        <v>10113.67</v>
-      </c>
-      <c r="F52" s="45">
-        <f>F51</f>
-        <v/>
-      </c>
-      <c r="G52" s="44" t="inlineStr">
-        <is>
-          <t>17/08 ✅ - שולם בניכוי 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1" s="131">
-      <c r="A53" s="43" t="n"/>
       <c r="B53" s="44" t="n"/>
       <c r="C53" s="44" t="n"/>
-      <c r="D53" s="45" t="n"/>
-      <c r="E53" s="45" t="n"/>
-      <c r="F53" s="45" t="n"/>
-      <c r="G53" s="44" t="n"/>
+      <c r="D53" s="45" t="n">
+        <v>10377.51</v>
+      </c>
+      <c r="E53" s="45" t="n">
+        <v>10113.67</v>
+      </c>
+      <c r="F53" s="45">
+        <f>F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="44" t="inlineStr">
+        <is>
+          <t>17/08 ✅ - שולם בניכוי 3%</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="131">
-      <c r="A54" s="72" t="inlineStr">
+      <c r="A54" s="43" t="n"/>
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="45" t="n"/>
+      <c r="G54" s="44" t="n"/>
+    </row>
+    <row r="55" ht="14.25" customHeight="1" s="131">
+      <c r="A55" s="72" t="inlineStr">
         <is>
           <t>פניני התכלת   |   מועד תשלום: ה-20 לחודש</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1" s="131">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="56" ht="14.25" customHeight="1" s="131">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1" s="131">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="n">
-        <v>90088</v>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="n">
-        <v>71026.56</v>
-      </c>
-      <c r="E56" s="24" t="n">
-        <v>69822.72</v>
-      </c>
-      <c r="F56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="30" t="inlineStr">
-        <is>
-          <t>19/08 ✅ שולם (ניכוי 2%, נטו 69,822.72)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="131">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט</t>
+          <t>יולי</t>
         </is>
       </c>
       <c r="B57" s="20" t="n">
-        <v>90110</v>
+        <v>90088</v>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D57" s="23" t="n">
-        <v>94093.2</v>
+        <v>71026.56</v>
       </c>
       <c r="E57" s="24" t="n">
-        <v>92498.39999999999</v>
+        <v>69822.72</v>
       </c>
       <c r="F57" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="30" t="inlineStr">
         <is>
+          <t>19/08 ✅ שולם (ניכוי 2%, נטו 69,822.72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customHeight="1" s="131">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>אוגוסט</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>90110</v>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>94093.2</v>
+      </c>
+      <c r="E58" s="24" t="n">
+        <v>92498.39999999999</v>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
+        <is>
           <t>22/09 ✅ שולם (ניכוי במקור 2% 1,594.80, נטו 92,498.40)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1" s="131">
-      <c r="A58" s="43" t="inlineStr">
+    <row r="59" ht="14.25" customHeight="1" s="131">
+      <c r="A59" s="43" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B58" s="44" t="n"/>
-      <c r="C58" s="44" t="n"/>
-      <c r="D58" s="45">
-        <f>SUM(D56:D57)</f>
-        <v/>
-      </c>
-      <c r="E58" s="45">
-        <f>SUM(E56:E57)</f>
-        <v/>
-      </c>
-      <c r="F58" s="45">
-        <f>SUM(F56:F57)</f>
-        <v/>
-      </c>
-      <c r="G58" s="44" t="n"/>
-    </row>
-    <row r="59" ht="14.25" customHeight="1" s="131"/>
+      <c r="B59" s="44" t="n"/>
+      <c r="C59" s="44" t="n"/>
+      <c r="D59" s="45">
+        <f>SUM(D57:D58)</f>
+        <v/>
+      </c>
+      <c r="E59" s="45">
+        <f>SUM(E57:E58)</f>
+        <v/>
+      </c>
+      <c r="F59" s="45">
+        <f>SUM(F57:F58)</f>
+        <v/>
+      </c>
+      <c r="G59" s="44" t="n"/>
+    </row>
     <row r="60" ht="14.25" customHeight="1" s="131"/>
-    <row r="61" ht="14.25" customHeight="1" s="131">
-      <c r="A61" s="72" t="inlineStr">
+    <row r="61" ht="14.25" customHeight="1" s="131"/>
+    <row r="62" ht="14.25" customHeight="1" s="131">
+      <c r="A62" s="72" t="inlineStr">
         <is>
           <t>BMG Human Resources and Placement  |  ח.פ. 516886835</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1" s="131">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="63" ht="14.25" customHeight="1" s="131">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1" s="131">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="64" ht="14.25" customHeight="1" s="131">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>ינואר</t>
         </is>
       </c>
-      <c r="B63" s="20" t="n"/>
-      <c r="C63" s="20" t="n"/>
-      <c r="D63" s="23" t="n">
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="24" t="n">
+      <c r="E64" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="29">
-        <f>D63-E63</f>
-        <v/>
-      </c>
-      <c r="G63" s="30" t="n"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1" s="131">
-      <c r="A64" s="43" t="inlineStr">
-        <is>
-          <t>פברואר</t>
-        </is>
-      </c>
-      <c r="B64" s="44" t="n">
-        <v>2137</v>
-      </c>
-      <c r="C64" s="44" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="D64" s="45" t="n">
-        <v>134971.4</v>
-      </c>
-      <c r="E64" s="45" t="n">
-        <v>130511</v>
-      </c>
-      <c r="F64" s="45">
+      <c r="F64" s="29">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="44" t="inlineStr">
-        <is>
-          <t>03/04 חלקי</t>
-        </is>
-      </c>
+      <c r="G64" s="30" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="131">
       <c r="A65" s="43" t="inlineStr">
         <is>
-          <t>מרץ</t>
+          <t>פברואר</t>
         </is>
       </c>
       <c r="B65" s="44" t="n">
-        <v>2154</v>
+        <v>2137</v>
       </c>
       <c r="C65" s="44" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="D65" s="45" t="n">
-        <v>204776.99</v>
+        <v>134971.4</v>
       </c>
       <c r="E65" s="45" t="n">
-        <v>204776.99</v>
+        <v>130511</v>
       </c>
       <c r="F65" s="45">
         <f>D65-E65</f>
@@ -2476,149 +2478,149 @@
       </c>
       <c r="G65" s="44" t="inlineStr">
         <is>
+          <t>03/04 חלקי</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="14.25" customHeight="1" s="131">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>מרץ</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="n">
+        <v>2154</v>
+      </c>
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="n">
+        <v>204776.99</v>
+      </c>
+      <c r="E66" s="45" t="n">
+        <v>204776.99</v>
+      </c>
+      <c r="F66" s="45">
+        <f>D66-E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="44" t="inlineStr">
+        <is>
           <t>20/05 ✅</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="14.25" customHeight="1" s="131">
-      <c r="A66" s="72" t="inlineStr">
+    <row r="67" ht="14.25" customHeight="1" s="131">
+      <c r="A67" s="72" t="inlineStr">
         <is>
           <t>אפריל</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B67" s="2" t="n">
         <v>2204</v>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="D66" s="73" t="n">
+      <c r="D67" s="73" t="n">
         <v>164619.44</v>
       </c>
-      <c r="E66" s="73" t="n">
+      <c r="E67" s="73" t="n">
         <v>144703.45</v>
       </c>
-      <c r="F66" s="73">
-        <f>D66-E66</f>
-        <v/>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="F67" s="73">
+        <f>D67-E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>13/07 חלקי</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14.25" customHeight="1" s="131">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="68" ht="14.25" customHeight="1" s="131">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>מאי</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B68" s="3" t="n">
         <v>1101</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>102027.52</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>102027.52</v>
       </c>
-      <c r="F67" s="3">
-        <f>D67-E67</f>
-        <v/>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="F68" s="3">
+        <f>D68-E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>30/06 ✅</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1" s="131">
-      <c r="A68" s="14" t="inlineStr">
+    <row r="69" ht="14.25" customHeight="1" s="131">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>יוני</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n">
+      <c r="B69" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="C68" s="20" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D68" s="23" t="n">
+      <c r="D69" s="23" t="n">
         <v>92764.64</v>
       </c>
-      <c r="E68" s="24" t="n">
+      <c r="E69" s="24" t="n">
         <v>92764.64</v>
       </c>
-      <c r="F68" s="29">
-        <f>D68-E68</f>
-        <v/>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="F69" s="29">
+        <f>D69-E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>31/07 חלקי + 10/08 השלמה ✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="14.25" customHeight="1" s="131">
-      <c r="A69" s="43" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
-      <c r="B69" s="44" t="n">
-        <v>3006</v>
-      </c>
-      <c r="C69" s="44" t="inlineStr">
-        <is>
-          <t>30/07/2026</t>
-        </is>
-      </c>
-      <c r="D69" s="45" t="n">
-        <v>94801.78999999999</v>
-      </c>
-      <c r="E69" s="45" t="n">
-        <v>94801.78999999999</v>
-      </c>
-      <c r="F69" s="45">
-        <f>D69-E69</f>
-        <v/>
-      </c>
-      <c r="G69" s="44" t="inlineStr">
-        <is>
-          <t>20/08 ✅ שולם</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1" s="131">
       <c r="A70" s="43" t="inlineStr">
         <is>
-          <t>אוגוסט</t>
+          <t>יולי</t>
         </is>
       </c>
       <c r="B70" s="44" t="n">
-        <v>4076</v>
-      </c>
-      <c r="C70" s="74" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
+        <v>3006</v>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="D70" s="45" t="n">
-        <v>69702.00999999999</v>
+        <v>94801.78999999999</v>
       </c>
       <c r="E70" s="45" t="n">
-        <v>69702.00999999999</v>
+        <v>94801.78999999999</v>
       </c>
       <c r="F70" s="45">
         <f>D70-E70</f>
@@ -2626,129 +2628,129 @@
       </c>
       <c r="G70" s="44" t="inlineStr">
         <is>
-          <t>05/10 ✅ שולם במלואו (חן 4076) - 69,702.01 ₪</t>
+          <t>20/08 ✅ שולם</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="131">
       <c r="A71" s="43" t="inlineStr">
         <is>
+          <t>אוגוסט</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="n">
+        <v>4076</v>
+      </c>
+      <c r="C71" s="74" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="n">
+        <v>69702.00999999999</v>
+      </c>
+      <c r="E71" s="45" t="n">
+        <v>69702.00999999999</v>
+      </c>
+      <c r="F71" s="45">
+        <f>D71-E71</f>
+        <v/>
+      </c>
+      <c r="G71" s="44" t="inlineStr">
+        <is>
+          <t>05/10 ✅ שולם במלואו (חן 4076) - 69,702.01 ₪</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14.25" customHeight="1" s="131">
+      <c r="A72" s="43" t="inlineStr">
+        <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B71" s="44" t="n"/>
-      <c r="C71" s="44" t="n"/>
-      <c r="D71" s="45">
-        <f>SUM(D63:D70)</f>
-        <v/>
-      </c>
-      <c r="E71" s="45">
-        <f>SUM(E63:E70)</f>
-        <v/>
-      </c>
-      <c r="F71" s="45">
-        <f>SUM(F63:F70)</f>
-        <v/>
-      </c>
-      <c r="G71" s="44" t="inlineStr">
+      <c r="B72" s="44" t="n"/>
+      <c r="C72" s="44" t="n"/>
+      <c r="D72" s="45">
+        <f>SUM(D64:D71)</f>
+        <v/>
+      </c>
+      <c r="E72" s="45">
+        <f>SUM(E64:E71)</f>
+        <v/>
+      </c>
+      <c r="F72" s="45">
+        <f>SUM(F64:F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="44" t="inlineStr">
         <is>
           <t>⚠️ רק פברואר+אפריל לא נכללים בסה"כ למטה (ממתין לכרטסת) - יולי מעודכן ונכלל</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="14.25" customHeight="1" s="131">
-      <c r="A72" s="72" t="inlineStr">
+    <row r="73" ht="14.25" customHeight="1" s="131">
+      <c r="A73" s="72" t="inlineStr">
         <is>
           <t>שי-לי כח אדם בע"מ  |  ע.מ. 515379725   |   מועד תשלום: ה-25 לחודש</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="14.25" customHeight="1" s="131">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="14.25" customHeight="1" s="131">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="14.25" customHeight="1" s="131">
-      <c r="A74" s="14" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
-      <c r="B74" s="20" t="n">
-        <v>230673</v>
-      </c>
-      <c r="C74" s="20" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="D74" s="23" t="n">
-        <v>44156</v>
-      </c>
-      <c r="E74" s="24" t="n">
-        <v>44156</v>
-      </c>
-      <c r="F74" s="29">
-        <f>D74-E74</f>
-        <v/>
-      </c>
-      <c r="G74" s="30" t="inlineStr">
-        <is>
-          <t>26/08 ⏳ שולם, טרם סופי</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1" s="131">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>אוגוסט</t>
+          <t>יולי</t>
         </is>
       </c>
       <c r="B75" s="20" t="n">
-        <v>230703</v>
-      </c>
-      <c r="C75" s="38" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
+        <v>230673</v>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D75" s="23" t="n">
-        <v>67944</v>
+        <v>44156</v>
       </c>
       <c r="E75" s="24" t="n">
-        <v>67944</v>
+        <v>44156</v>
       </c>
       <c r="F75" s="29">
         <f>D75-E75</f>
@@ -2756,27 +2758,29 @@
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>24/09 ✅ שולם במלואו (חן 230703)</t>
+          <t>26/08 ⏳ שולם, טרם סופי</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1" s="131">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>ספטמבר</t>
+          <t>אוגוסט</t>
         </is>
       </c>
       <c r="B76" s="20" t="n">
-        <v>230747</v>
-      </c>
-      <c r="C76" s="59" t="n">
-        <v>46295</v>
+        <v>230703</v>
+      </c>
+      <c r="C76" s="38" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="D76" s="23" t="n">
-        <v>44571</v>
+        <v>67944</v>
       </c>
       <c r="E76" s="24" t="n">
-        <v>0</v>
+        <v>67944</v>
       </c>
       <c r="F76" s="29">
         <f>D76-E76</f>
@@ -2784,133 +2788,131 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
+          <t>24/09 ✅ שולם במלואו (חן 230703)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="14.25" customHeight="1" s="131">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n">
+        <v>230747</v>
+      </c>
+      <c r="C77" s="59" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="29">
+        <f>D77-E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
           <t>⏳ לתשלום ב-25/10/2026 (532 שעות × 71 ₪ + מע"מ; אתר הקליר 10, ירושלים)</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="14.25" customHeight="1" s="131">
-      <c r="A77" s="43" t="inlineStr">
-        <is>
-          <t>סה"כ</t>
-        </is>
-      </c>
-      <c r="B77" s="44" t="n"/>
-      <c r="C77" s="44" t="n"/>
-      <c r="D77" s="45">
-        <f>SUM(D74:D76)</f>
-        <v/>
-      </c>
-      <c r="E77" s="45">
-        <f>SUM(E74:E76)</f>
-        <v/>
-      </c>
-      <c r="F77" s="45">
-        <f>SUM(F74:F76)</f>
-        <v/>
-      </c>
-      <c r="G77" s="44" t="n"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" s="131">
       <c r="A78" s="43" t="inlineStr">
         <is>
-          <t>ד.יוחאי בע"מ  |  עוסק מורשה 516890944   |   מועד תשלום: ה-20 לחודש</t>
+          <t>סה"כ</t>
         </is>
       </c>
       <c r="B78" s="44" t="n"/>
       <c r="C78" s="44" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="D78" s="45">
+        <f>SUM(D75:D77)</f>
+        <v/>
+      </c>
+      <c r="E78" s="45">
+        <f>SUM(E75:E77)</f>
+        <v/>
+      </c>
+      <c r="F78" s="45">
+        <f>SUM(F75:F77)</f>
+        <v/>
+      </c>
       <c r="G78" s="44" t="n"/>
     </row>
     <row r="79" ht="14.25" customHeight="1" s="131">
       <c r="A79" s="43" t="inlineStr">
         <is>
-          <t>חודש עבודה</t>
-        </is>
-      </c>
-      <c r="B79" s="44" t="inlineStr">
-        <is>
-          <t>מס׳ חשבונית</t>
-        </is>
-      </c>
-      <c r="C79" s="44" t="inlineStr">
-        <is>
-          <t>תאריך</t>
-        </is>
-      </c>
-      <c r="D79" s="45" t="inlineStr">
-        <is>
-          <t>גולמי (₪)</t>
-        </is>
-      </c>
-      <c r="E79" s="45" t="inlineStr">
-        <is>
-          <t>שולם (₪)</t>
-        </is>
-      </c>
-      <c r="F79" s="45" t="inlineStr">
-        <is>
-          <t>יתרה (₪)</t>
-        </is>
-      </c>
-      <c r="G79" s="44" t="inlineStr">
-        <is>
-          <t>תאריך תשלום</t>
-        </is>
-      </c>
+          <t>ד.יוחאי בע"מ  |  עוסק מורשה 516890944   |   מועד תשלום: ה-20 לחודש</t>
+        </is>
+      </c>
+      <c r="B79" s="44" t="n"/>
+      <c r="C79" s="44" t="n"/>
+      <c r="D79" s="45" t="n"/>
+      <c r="E79" s="45" t="n"/>
+      <c r="F79" s="45" t="n"/>
+      <c r="G79" s="44" t="n"/>
     </row>
     <row r="80" ht="14.25" customHeight="1" s="131">
       <c r="A80" s="43" t="inlineStr">
         <is>
-          <t>אוגוסט</t>
+          <t>חודש עבודה</t>
         </is>
       </c>
       <c r="B80" s="44" t="inlineStr">
         <is>
-          <t>IN264000106</t>
-        </is>
-      </c>
-      <c r="C80" s="74" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="D80" s="45" t="n">
-        <v>35758.81</v>
-      </c>
-      <c r="E80" s="45" t="n">
-        <v>35758.81</v>
-      </c>
-      <c r="F80" s="45">
-        <f>D80-E80</f>
-        <v/>
+          <t>מס׳ חשבונית</t>
+        </is>
+      </c>
+      <c r="C80" s="44" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="D80" s="45" t="inlineStr">
+        <is>
+          <t>גולמי (₪)</t>
+        </is>
+      </c>
+      <c r="E80" s="45" t="inlineStr">
+        <is>
+          <t>שולם (₪)</t>
+        </is>
+      </c>
+      <c r="F80" s="45" t="inlineStr">
+        <is>
+          <t>יתרה (₪)</t>
+        </is>
       </c>
       <c r="G80" s="44" t="inlineStr">
         <is>
-          <t>22/09 ✅ שולם במלואו</t>
+          <t>תאריך תשלום</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1" s="131">
       <c r="A81" s="43" t="inlineStr">
         <is>
-          <t>ספטמבר</t>
+          <t>אוגוסט</t>
         </is>
       </c>
       <c r="B81" s="44" t="inlineStr">
         <is>
-          <t>IN264000117</t>
-        </is>
-      </c>
-      <c r="C81" s="125" t="n">
-        <v>46295</v>
+          <t>IN264000106</t>
+        </is>
+      </c>
+      <c r="C81" s="74" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="D81" s="45" t="n">
-        <v>35432.57</v>
+        <v>35758.81</v>
       </c>
       <c r="E81" s="45" t="n">
-        <v>0</v>
+        <v>35758.81</v>
       </c>
       <c r="F81" s="45">
         <f>D81-E81</f>
@@ -2918,292 +2920,321 @@
       </c>
       <c r="G81" s="44" t="inlineStr">
         <is>
-          <t>⏳ לתשלום ב-20/10/2026 · 321.05 שעות ספטמבר + 96 שעות השלמה לתקן = 417.05 × 72 ₪ = 30,027.60 + מע"מ 5,404.97</t>
+          <t>22/09 ✅ שולם במלואו</t>
         </is>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1" s="131">
       <c r="A82" s="43" t="inlineStr">
         <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B82" s="44" t="inlineStr">
+        <is>
+          <t>IN264000117</t>
+        </is>
+      </c>
+      <c r="C82" s="125" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D82" s="45" t="n">
+        <v>35432.57</v>
+      </c>
+      <c r="E82" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="45">
+        <f>D82-E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="44" t="inlineStr">
+        <is>
+          <t>⏳ לתשלום ב-20/10/2026 · 321.05 שעות ספטמבר + 96 שעות השלמה לתקן = 417.05 × 72 ₪ = 30,027.60 + מע"מ 5,404.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="14.25" customHeight="1" s="131">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B82" s="44" t="n"/>
-      <c r="C82" s="44" t="n"/>
-      <c r="D82" s="45">
-        <f>SUM(D80:D81)</f>
-        <v/>
-      </c>
-      <c r="E82" s="45">
-        <f>SUM(E80:E81)</f>
-        <v/>
-      </c>
-      <c r="F82" s="45">
-        <f>SUM(F80:F81)</f>
-        <v/>
-      </c>
-      <c r="G82" s="44" t="n"/>
-    </row>
-    <row r="83" ht="14.25" customHeight="1" s="131">
-      <c r="A83" s="43" t="n"/>
       <c r="B83" s="44" t="n"/>
       <c r="C83" s="44" t="n"/>
-      <c r="D83" s="45" t="n"/>
-      <c r="E83" s="45" t="n"/>
-      <c r="F83" s="45" t="n"/>
+      <c r="D83" s="45">
+        <f>SUM(D81:D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="45">
+        <f>SUM(E81:E82)</f>
+        <v/>
+      </c>
+      <c r="F83" s="45">
+        <f>SUM(F81:F82)</f>
+        <v/>
+      </c>
       <c r="G83" s="44" t="n"/>
     </row>
     <row r="84" ht="14.25" customHeight="1" s="131">
-      <c r="A84" s="72" t="inlineStr">
+      <c r="A84" s="43" t="n"/>
+      <c r="B84" s="44" t="n"/>
+      <c r="C84" s="44" t="n"/>
+      <c r="D84" s="45" t="n"/>
+      <c r="E84" s="45" t="n"/>
+      <c r="F84" s="45" t="n"/>
+      <c r="G84" s="44" t="n"/>
+    </row>
+    <row r="85" ht="14.25" customHeight="1" s="131">
+      <c r="A85" s="72" t="inlineStr">
         <is>
           <t>שרף (ד.י שרף השקעות)   |   ירון 054-6477110   |   ✅ שולם 09/09/2026 - החשבונית עצמה טרם התקבלה</t>
         </is>
       </c>
-      <c r="B84" s="77" t="n"/>
-      <c r="C84" s="77" t="n"/>
-      <c r="D84" s="79" t="n"/>
-      <c r="E84" s="79" t="n"/>
-      <c r="F84" s="79" t="n"/>
-      <c r="G84" s="77" t="n"/>
-    </row>
-    <row r="85" ht="14.25" customHeight="1" s="131">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="B85" s="77" t="n"/>
+      <c r="C85" s="77" t="n"/>
+      <c r="D85" s="79" t="n"/>
+      <c r="E85" s="79" t="n"/>
+      <c r="F85" s="79" t="n"/>
+      <c r="G85" s="77" t="n"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1" s="131">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D85" s="81" t="inlineStr">
+      <c r="D86" s="81" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E85" s="81" t="inlineStr">
+      <c r="E86" s="81" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F85" s="81" t="inlineStr">
+      <c r="F86" s="81" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="14.25" customHeight="1" s="131">
-      <c r="A86" s="14" t="inlineStr">
+    <row r="87" ht="14.25" customHeight="1" s="131">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t>אוגוסט</t>
         </is>
       </c>
-      <c r="B86" s="20" t="inlineStr">
+      <c r="B87" s="20" t="inlineStr">
         <is>
           <t>ממתין לקבלת חשבונית</t>
         </is>
       </c>
-      <c r="C86" s="38" t="inlineStr">
+      <c r="C87" s="38" t="inlineStr">
         <is>
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="D86" s="23" t="n">
+      <c r="D87" s="23" t="n">
         <v>75065</v>
       </c>
-      <c r="E86" s="23" t="n">
+      <c r="E87" s="23" t="n">
         <v>75065</v>
       </c>
-      <c r="F86" s="23">
-        <f>D86-E86</f>
-        <v/>
-      </c>
-      <c r="G86" s="20" t="inlineStr">
+      <c r="F87" s="23">
+        <f>D87-E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="20" t="inlineStr">
         <is>
           <t>✅ שולם 09/09/2026 בהעברה דיגיטלית - 75,065 ₪ (סכום מאומת מול הבנק, לא אומדן). עדיין יש לקבל את מסמך החשבונית עצמו מהתאגיד</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="14.25" customHeight="1" s="131">
-      <c r="A87" s="43" t="inlineStr">
+    <row r="88" ht="14.25" customHeight="1" s="131">
+      <c r="A88" s="43" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B87" s="44" t="n"/>
-      <c r="C87" s="44" t="n"/>
-      <c r="D87" s="45">
-        <f>D86</f>
-        <v/>
-      </c>
-      <c r="E87" s="45">
-        <f>E86</f>
-        <v/>
-      </c>
-      <c r="F87" s="45">
-        <f>F86</f>
-        <v/>
-      </c>
-      <c r="G87" s="44" t="n"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1" s="131">
-      <c r="A88" s="72" t="inlineStr">
+      <c r="B88" s="44" t="n"/>
+      <c r="C88" s="44" t="n"/>
+      <c r="D88" s="45">
+        <f>D87</f>
+        <v/>
+      </c>
+      <c r="E88" s="45">
+        <f>E87</f>
+        <v/>
+      </c>
+      <c r="F88" s="45">
+        <f>F87</f>
+        <v/>
+      </c>
+      <c r="G88" s="44" t="n"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1" s="131">
+      <c r="A89" s="72" t="inlineStr">
         <is>
           <t>ג.ד. קלמרה הנדסה ובנייה בע"מ   |   ח.פ. 516489689</t>
         </is>
       </c>
-      <c r="B88" s="77" t="n"/>
-      <c r="C88" s="77" t="n"/>
-      <c r="D88" s="79" t="n"/>
-      <c r="E88" s="79" t="n"/>
-      <c r="F88" s="79" t="n"/>
-      <c r="G88" s="77" t="n"/>
-    </row>
-    <row r="89" ht="14.25" customHeight="1" s="131">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="B89" s="77" t="n"/>
+      <c r="C89" s="77" t="n"/>
+      <c r="D89" s="79" t="n"/>
+      <c r="E89" s="79" t="n"/>
+      <c r="F89" s="79" t="n"/>
+      <c r="G89" s="77" t="n"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1" s="131">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>חודש עבודה</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>מס׳ חשבונית</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="D89" s="81" t="inlineStr">
+      <c r="D90" s="81" t="inlineStr">
         <is>
           <t>גולמי (₪)</t>
         </is>
       </c>
-      <c r="E89" s="81" t="inlineStr">
+      <c r="E90" s="81" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="F89" s="81" t="inlineStr">
+      <c r="F90" s="81" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>תאריך תשלום</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="14.25" customHeight="1" s="131">
-      <c r="A90" s="14" t="inlineStr">
+    <row r="91" ht="14.25" customHeight="1" s="131">
+      <c r="A91" s="14" t="inlineStr">
         <is>
           <t>אוגוסט</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n">
+      <c r="B91" s="20" t="n">
         <v>20019</v>
       </c>
-      <c r="C90" s="38" t="inlineStr">
+      <c r="C91" s="38" t="inlineStr">
         <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="D90" s="23" t="n">
+      <c r="D91" s="23" t="n">
         <v>4085</v>
       </c>
-      <c r="E90" s="23" t="n">
+      <c r="E91" s="23" t="n">
         <v>4085</v>
       </c>
-      <c r="F90" s="23">
-        <f>D90-E90</f>
-        <v/>
-      </c>
-      <c r="G90" s="20" t="inlineStr">
+      <c r="F91" s="23">
+        <f>D91-E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
         <is>
           <t>22/09 ✅ שולם</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="14.25" customHeight="1" s="131">
-      <c r="A91" s="43" t="inlineStr">
+    <row r="92" ht="14.25" customHeight="1" s="131">
+      <c r="A92" s="43" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B91" s="44" t="n"/>
-      <c r="C91" s="44" t="n"/>
-      <c r="D91" s="45" t="n">
-        <v>4085</v>
-      </c>
-      <c r="E91" s="45" t="n">
-        <v>4085</v>
-      </c>
-      <c r="F91" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="44" t="n"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1" s="131">
-      <c r="A92" s="43" t="n"/>
       <c r="B92" s="44" t="n"/>
       <c r="C92" s="44" t="n"/>
-      <c r="D92" s="45" t="n"/>
-      <c r="E92" s="45" t="n"/>
-      <c r="F92" s="45" t="n"/>
+      <c r="D92" s="45" t="n">
+        <v>4085</v>
+      </c>
+      <c r="E92" s="45" t="n">
+        <v>4085</v>
+      </c>
+      <c r="F92" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="G92" s="44" t="n"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1" s="131"/>
-    <row r="94" ht="21.75" customHeight="1" s="131">
-      <c r="A94" s="139" t="inlineStr">
+    <row r="93" ht="14.25" customHeight="1" s="131">
+      <c r="A93" s="43" t="n"/>
+      <c r="B93" s="44" t="n"/>
+      <c r="C93" s="44" t="n"/>
+      <c r="D93" s="45" t="n"/>
+      <c r="E93" s="45" t="n"/>
+      <c r="F93" s="45" t="n"/>
+      <c r="G93" s="44" t="n"/>
+    </row>
+    <row r="94" ht="14.25" customHeight="1" s="131"/>
+    <row r="95" ht="21.75" customHeight="1" s="131">
+      <c r="A95" s="139" t="inlineStr">
         <is>
           <t>💰  סך חוב פתוח לכל התאגידים   (✱ לא כולל BMG פברואר+אפריל | לא כולל פאנג יוני 125,000 - צ׳ק 5000346 ב-25/10)</t>
         </is>
       </c>
-      <c r="D94" s="87">
-        <f>F15+F28+(F40-125000)+F47+F52+F58+(F71-4460.4-19915.99)+F77+F82+F87+F91</f>
-        <v/>
-      </c>
-      <c r="E94" s="88" t="n"/>
-      <c r="F94" s="88" t="n"/>
-      <c r="G94" s="88" t="n"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1" s="131"/>
-    <row r="96" ht="14.25" customHeight="1" s="131">
-      <c r="A96" s="138" t="inlineStr">
+      <c r="D95" s="87">
+        <f>F15+F28+(F41-125000)+F48+F53+F59+(F72-4460.4-19915.99)+F78+F83+F88+F92</f>
+        <v/>
+      </c>
+      <c r="E95" s="88" t="n"/>
+      <c r="F95" s="88" t="n"/>
+      <c r="G95" s="88" t="n"/>
+    </row>
+    <row r="96" ht="14.25" customHeight="1" s="131"/>
+    <row r="97" ht="14.25" customHeight="1" s="131">
+      <c r="A97" s="138" t="inlineStr">
         <is>
           <t>✱ יתרת פאנג יוני: צ׳ק 24/09/2026 ירד ✅ · נותר צ׳ק 25/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="14.25" customHeight="1" s="131">
-      <c r="A97" s="58" t="inlineStr">
+    <row r="98" ht="14.25" customHeight="1" s="131">
+      <c r="A98" s="58" t="inlineStr">
         <is>
           <t>✅ כל חשבוניות אוגוסט התקבלו. שולמו: פסגת ליאם, שרף (09/09), פניני התכלת, ד.יוחאי, אחים לימור, ג.ד קלמרה, פוגין (22/09), שי-לי (24/09), BMG (05/10). נותרה לתשלום: פאנג. ✅ פסגת ליאם ספטמבר (50156) שולם 06/10 - 12,685.71 ₪. שרף - עדיין ממתין למסמך החשבונית עצמו. ⏳ פוגין ספטמבר (01/000938) - 18,262.90 ₪ לתשלום 25/10. ⏳ שי-לי ספטמבר (230747) - 44,571 ₪ לתשלום 25/10. ⏳ אחים לימור ספטמבר (חשבון עסקה 8052) - 107,834.30 ₪.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="14.25" customHeight="1" s="131"/>
-    <row r="99" ht="14.25" customHeight="1" s="131">
-      <c r="A99" s="89" t="inlineStr">
+    <row r="99" ht="14.25" customHeight="1" s="131"/>
+    <row r="100" ht="14.25" customHeight="1" s="131">
+      <c r="A100" s="89" t="inlineStr">
         <is>
           <t>מועדי תשלום קבועים לתאגידים: עוצמת התמרון - ה-15 לחודש · פניני התכלת - ה-20 לחודש · יוחאי - ה-20 לחודש · שי-לי - ה-25 לחודש · פוגין - ה-25 לחודש</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="14.25" customHeight="1" s="131"/>
     <row r="101" ht="14.25" customHeight="1" s="131"/>
     <row r="102" ht="14.25" customHeight="1" s="131"/>
     <row r="103" ht="14.25" customHeight="1" s="131"/>
@@ -4131,18 +4162,18 @@
     <row r="1025" ht="14.25" customHeight="1" s="131"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A96:G96"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A95:C95"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -17947,7 +17978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="41.375" customWidth="1" style="131" min="1" max="1"/>
@@ -18149,121 +18180,125 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="131">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>סה״כ חוב תאגידים - אוגוסט + ספטמבר</t>
-        </is>
-      </c>
-      <c r="D11" s="45">
-        <f>SUM(D6:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="99" t="n"/>
+      <c r="A11" s="90" t="inlineStr">
+        <is>
+          <t>פאנג</t>
+        </is>
+      </c>
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="C11" s="91" t="inlineStr">
+        <is>
+          <t>01/002772</t>
+        </is>
+      </c>
+      <c r="D11" s="92" t="n">
+        <v>301259.9</v>
+      </c>
+      <c r="E11" s="93" t="inlineStr">
+        <is>
+          <t>⏳ חשבונית מס 01/002772 מ-13/10/2026 · 255,305 + מע"מ 45,954.90 · אספקת כ"א 09.26 לאתרים שונים בירושלים · מועד תשלום טרם נקבע</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="131">
-      <c r="A12" s="140" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>סה״כ חוב תאגידים - אוגוסט + ספטמבר (כולל פאנג ספטמבר)</t>
+        </is>
+      </c>
+      <c r="D12" s="45">
+        <f>SUM(D6:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="99" t="n"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" s="131">
+      <c r="A13" s="140" t="inlineStr">
         <is>
           <t>👤  חוב אישי - שמואל מינסקי</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1" s="131">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="14.25" customHeight="1" s="131">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>סכום (₪)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1" s="131">
-      <c r="A14" s="90" t="inlineStr">
+      <c r="E14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="14.25" customHeight="1" s="131">
+      <c r="A15" s="90" t="inlineStr">
         <is>
           <t>התחשבנות אישית - הלוואות (ישראכרט+מגדל) + הוצאות מהכיס, טרם הוחזרו. נכון ל-13/10/2026: לפי הבנק עד 11/10 (כולל ישראכרט 02/10 1,309.24 + מגדל 11/10 2,240.25) = 18,739.68 הלוואות + מגדל 10/09 (2,187.32) לפי הלוח, חסר בדף הבנק. מקור: קובץ "התחשבנות שמואל מינסקי" (מתעדכן שם אוטומטית)</t>
         </is>
       </c>
-      <c r="B14" s="91" t="n"/>
-      <c r="C14" s="91" t="n"/>
-      <c r="D14" s="92" t="n">
+      <c r="B15" s="91" t="n"/>
+      <c r="C15" s="91" t="n"/>
+      <c r="D15" s="92" t="n">
         <v>23427</v>
       </c>
-      <c r="E14" s="93" t="n"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1" s="131"/>
-    <row r="16" ht="14.25" customHeight="1" s="131">
-      <c r="A16" s="103" t="n"/>
-      <c r="B16" s="58" t="n"/>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="58" t="n"/>
-      <c r="E16" s="58" t="n"/>
-    </row>
+      <c r="E15" s="93" t="n"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" s="131"/>
     <row r="17" ht="14.25" customHeight="1" s="131">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="103" t="n"/>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1" s="131">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>סכום (₪)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1" s="131">
-      <c r="A18" s="91" t="inlineStr">
-        <is>
-          <t>אוגוסט</t>
-        </is>
-      </c>
-      <c r="B18" s="90" t="inlineStr">
-        <is>
-          <t>פאנג – חשבונית 01/002721</t>
-        </is>
-      </c>
-      <c r="C18" s="92" t="n">
-        <v>208316.3</v>
-      </c>
-      <c r="D18" s="105" t="inlineStr">
-        <is>
-          <t>⏳ שולם 230,000 ב-07/10/2026 · היתרה ב-3 צ׳קים של 69,438 (26/11, 26/12, 26/01) · 🏢 כלול גם בחוב תאגידים למעלה</t>
-        </is>
-      </c>
-      <c r="E18" s="106" t="n"/>
+      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" s="131">
       <c r="A19" s="91" t="inlineStr">
         <is>
-          <t>אוקטובר</t>
+          <t>אוגוסט</t>
         </is>
       </c>
       <c r="B19" s="90" t="inlineStr">
         <is>
-          <t>שלום קבאסה – הפרשי מים וחשמל, דירת אשקלון</t>
+          <t>פאנג – חשבונית 01/002721</t>
         </is>
       </c>
       <c r="C19" s="92" t="n">
-        <v>4078</v>
+        <v>208316.3</v>
       </c>
       <c r="D19" s="105" t="inlineStr">
         <is>
-          <t>⏳ לתשלום (לפי שמואל, 07/10/2026). רק הפרשי מים וחשמל - ללא שכירות (שכירות אשקלון לא משולמת מספטמבר)</t>
+          <t>⏳ שולם 230,000 ב-07/10/2026 · היתרה ב-3 צ׳קים של 69,438 (26/11, 26/12, 26/01) · 🏢 כלול גם בחוב תאגידים למעלה</t>
         </is>
       </c>
       <c r="E19" s="106" t="n"/>
@@ -18271,20 +18306,20 @@
     <row r="20" ht="14.25" customHeight="1" s="131">
       <c r="A20" s="91" t="inlineStr">
         <is>
-          <t>ספטמבר</t>
+          <t>אוקטובר</t>
         </is>
       </c>
       <c r="B20" s="90" t="inlineStr">
         <is>
-          <t>פוגין – חשבונית 01/000938</t>
+          <t>שלום קבאסה – הפרשי מים וחשמל, דירת אשקלון</t>
         </is>
       </c>
       <c r="C20" s="92" t="n">
-        <v>18262.9</v>
+        <v>4078</v>
       </c>
       <c r="D20" s="105" t="inlineStr">
         <is>
-          <t>⏳ לתשלום 25/10/2026 · 🏢 כלול גם בחוב תאגידים למעלה</t>
+          <t>⏳ לתשלום (לפי שמואל, 07/10/2026). רק הפרשי מים וחשמל - ללא שכירות (שכירות אשקלון לא משולמת מספטמבר)</t>
         </is>
       </c>
       <c r="E20" s="106" t="n"/>
@@ -18297,11 +18332,11 @@
       </c>
       <c r="B21" s="90" t="inlineStr">
         <is>
-          <t>שי-לי – חשבונית 230747</t>
+          <t>פוגין – חשבונית 01/000938</t>
         </is>
       </c>
       <c r="C21" s="92" t="n">
-        <v>44571</v>
+        <v>18262.9</v>
       </c>
       <c r="D21" s="105" t="inlineStr">
         <is>
@@ -18313,20 +18348,20 @@
     <row r="22" ht="14.25" customHeight="1" s="131">
       <c r="A22" s="91" t="inlineStr">
         <is>
-          <t>אוקטובר</t>
+          <t>ספטמבר</t>
         </is>
       </c>
       <c r="B22" s="90" t="inlineStr">
         <is>
-          <t>ש. מינסקי יזמות</t>
+          <t>שי-לי – חשבונית 230747</t>
         </is>
       </c>
       <c r="C22" s="92" t="n">
-        <v>0</v>
+        <v>44571</v>
       </c>
       <c r="D22" s="105" t="inlineStr">
         <is>
-          <t>✅ שולם 13/10/2026 בצ׳ק 5000289 - 16,520 ₪ (כאן נרשם 16,250; גם התשלומים ב-13/07 וב-16/08 היו 16,520) · ✅ אושר ע"י שמואל 14/10</t>
+          <t>⏳ לתשלום 25/10/2026 · 🏢 כלול גם בחוב תאגידים למעלה</t>
         </is>
       </c>
       <c r="E22" s="106" t="n"/>
@@ -18334,20 +18369,20 @@
     <row r="23" ht="14.25" customHeight="1" s="131">
       <c r="A23" s="91" t="inlineStr">
         <is>
-          <t>ספטמבר</t>
+          <t>אוקטובר</t>
         </is>
       </c>
       <c r="B23" s="90" t="inlineStr">
         <is>
-          <t>אחים לימור – חשבון עסקה 8052</t>
+          <t>ש. מינסקי יזמות</t>
         </is>
       </c>
       <c r="C23" s="92" t="n">
-        <v>107834.3</v>
+        <v>0</v>
       </c>
       <c r="D23" s="105" t="inlineStr">
         <is>
-          <t>⏳ ממתין לתשלום · 🏢 כלול גם בחוב תאגידים למעלה</t>
+          <t>✅ שולם 13/10/2026 בצ׳ק 5000289 - 16,520 ₪ (כאן נרשם 16,250; גם התשלומים ב-13/07 וב-16/08 היו 16,520) · ✅ אושר ע"י שמואל 14/10</t>
         </is>
       </c>
       <c r="E23" s="106" t="n"/>
@@ -18360,15 +18395,15 @@
       </c>
       <c r="B24" s="90" t="inlineStr">
         <is>
-          <t>ד.יוחאי – חשבונית IN264000117</t>
+          <t>אחים לימור – חשבון עסקה 8052</t>
         </is>
       </c>
       <c r="C24" s="92" t="n">
-        <v>35432.57</v>
+        <v>107834.3</v>
       </c>
       <c r="D24" s="105" t="inlineStr">
         <is>
-          <t>⏳ לתשלום 20/10/2026 · 🏢 כלול גם בחוב תאגידים למעלה</t>
+          <t>⏳ ממתין לתשלום · 🏢 כלול גם בחוב תאגידים למעלה</t>
         </is>
       </c>
       <c r="E24" s="106" t="n"/>
@@ -18376,126 +18411,126 @@
     <row r="25" ht="14.25" customHeight="1" s="131">
       <c r="A25" s="91" t="inlineStr">
         <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B25" s="90" t="inlineStr">
+        <is>
+          <t>ד.יוחאי – חשבונית IN264000117</t>
+        </is>
+      </c>
+      <c r="C25" s="92" t="n">
+        <v>35432.57</v>
+      </c>
+      <c r="D25" s="105" t="inlineStr">
+        <is>
+          <t>⏳ לתשלום 20/10/2026 · 🏢 כלול גם בחוב תאגידים למעלה</t>
+        </is>
+      </c>
+      <c r="E25" s="106" t="n"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" s="131">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
           <t>יוני-אוגוסט</t>
         </is>
       </c>
-      <c r="B25" s="90" t="inlineStr">
+      <c r="B26" s="90" t="inlineStr">
         <is>
           <t>רז שרי ייבוא וסחר – חשבוניות 155, 158, 161 (תיווך/שכ"ט)</t>
         </is>
       </c>
-      <c r="C25" s="92" t="n">
+      <c r="C26" s="92" t="n">
         <v>12676.86</v>
       </c>
-      <c r="D25" s="105" t="inlineStr">
+      <c r="D26" s="105" t="inlineStr">
         <is>
           <t>⏳ פתוח - לא שולם (תשלום אחרון 15/06 על חן 152). 155: 4,573.68 (30/06) · 158: 4,014.48 (31/07) · 161: 4,088.70 (31/08). להעברה אחרי ניכוי במקור 5%: 12,139.70</t>
         </is>
       </c>
-      <c r="E25" s="106" t="n"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1" s="131">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="E26" s="106" t="n"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1" s="131">
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>ספטמבר</t>
+        </is>
+      </c>
+      <c r="B27" s="90" t="inlineStr">
+        <is>
+          <t>פאנג – חשבונית 01/002772</t>
+        </is>
+      </c>
+      <c r="C27" s="92" t="n">
+        <v>301259.9</v>
+      </c>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>⏳ מועד תשלום טרם נקבע · 🏢 כלול גם בחוב תאגידים למעלה</t>
+        </is>
+      </c>
+      <c r="E27" s="106" t="n"/>
+    </row>
+    <row r="28" ht="14.25" customHeight="1" s="131">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>סה״כ תזרים אוגוסט + ספטמבר</t>
         </is>
       </c>
-      <c r="C26" s="45">
-        <f>SUM(C18:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="99" t="n"/>
-      <c r="E26" s="99" t="n"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1" s="131"/>
-    <row r="28" ht="21.75" customHeight="1" s="131">
-      <c r="A28" s="139" t="inlineStr">
+      <c r="C28" s="45">
+        <f>SUM(C19:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="99" t="n"/>
+      <c r="E28" s="99" t="n"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" s="131"/>
+    <row r="30" ht="21.75" customHeight="1" s="131">
+      <c r="A30" s="139" t="inlineStr">
         <is>
           <t>💰  סה״כ ממתין לתשלום (יתרת פאנג אוגוסט + פוגין, שי-לי ואחים לימור ספטמבר + שלום קבאסה + ש. מינסקי יזמות + רז שרי)</t>
         </is>
       </c>
-      <c r="D28" s="87">
-        <f>D11+C19+C22+C25</f>
-        <v/>
-      </c>
-      <c r="E28" s="88" t="n"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1" s="131"/>
-    <row r="30" ht="14.25" customHeight="1" s="131">
-      <c r="A30" s="138" t="n"/>
+      <c r="D30" s="87">
+        <f>D12+C20+C23+C26</f>
+        <v/>
+      </c>
+      <c r="E30" s="88" t="n"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="131"/>
     <row r="32" ht="14.25" customHeight="1" s="131">
-      <c r="A32" s="78" t="inlineStr">
+      <c r="A32" s="138" t="n"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1" s="131"/>
+    <row r="34" ht="14.25" customHeight="1" s="131">
+      <c r="A34" s="78" t="inlineStr">
         <is>
           <t>💰  לקוחות חייבים לנו</t>
         </is>
       </c>
-      <c r="B32" s="80" t="n"/>
-      <c r="C32" s="80" t="n"/>
-      <c r="D32" s="80" t="n"/>
-    </row>
-    <row r="33" ht="14.25" customHeight="1" s="131">
-      <c r="A33" s="107" t="inlineStr">
+      <c r="B34" s="80" t="n"/>
+      <c r="C34" s="80" t="n"/>
+      <c r="D34" s="80" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" s="131">
+      <c r="A35" s="107" t="inlineStr">
         <is>
           <t>לקוח</t>
         </is>
       </c>
-      <c r="B33" s="107" t="inlineStr">
+      <c r="B35" s="107" t="inlineStr">
         <is>
           <t>אמצעי תשלום</t>
         </is>
       </c>
-      <c r="C33" s="107" t="inlineStr">
+      <c r="C35" s="107" t="inlineStr">
         <is>
           <t>סכום (₪)</t>
         </is>
       </c>
-      <c r="D33" s="108" t="inlineStr">
+      <c r="D35" s="108" t="inlineStr">
         <is>
           <t>הערות / סטטוס</t>
-        </is>
-      </c>
-      <c r="E33" s="109" t="n"/>
-    </row>
-    <row r="34" ht="14.25" customHeight="1" s="131">
-      <c r="A34" s="110" t="inlineStr">
-        <is>
-          <t>נטליה הודיה</t>
-        </is>
-      </c>
-      <c r="B34" s="110" t="inlineStr">
-        <is>
-          <t>מזומן / נחשון</t>
-        </is>
-      </c>
-      <c r="C34" s="111" t="n">
-        <v>15803.8</v>
-      </c>
-      <c r="D34" s="112" t="inlineStr">
-        <is>
-          <t>⏳ שולמו עד כה 7,000 ₪ במזומן: 4,000 ₪ + 3,000 ₪ ביום שלישי 08/09/2026. 💵 המזומן לא נכנס לבנק ולכן אינו ביתרת הבנק. ⚠️ לאימות: ה-4,000 נרשמו בדוח שהיה "נכון ל-09/09" - יש לוודא שזה תשלום נפרד מה-3,000 של 08/09 ולא כפילות. ממשיך בתשלומים שבועיים עד לסגירת היתרה</t>
-        </is>
-      </c>
-      <c r="E34" s="109" t="n"/>
-    </row>
-    <row r="35" ht="14.25" customHeight="1" s="131">
-      <c r="A35" s="110" t="inlineStr">
-        <is>
-          <t>מצודת השלום</t>
-        </is>
-      </c>
-      <c r="B35" s="110" t="inlineStr">
-        <is>
-          <t>עמלות ניכיון צ׳קים באופל בלאנס - לחיוב הלקוח</t>
-        </is>
-      </c>
-      <c r="C35" s="111" t="n">
-        <v>2367</v>
-      </c>
-      <c r="D35" s="112" t="inlineStr">
-        <is>
-          <t>עמלת ניכיון 1,458 (צ׳ק 14291, קבלה 1857 מ-22/07) + עמלת ניכיון 909 (צ׳קים 14297+14298, קבלה 1969 מ-23/08) = 2,367</t>
         </is>
       </c>
       <c r="E35" s="109" t="n"/>
@@ -18503,20 +18538,20 @@
     <row r="36" ht="14.25" customHeight="1" s="131">
       <c r="A36" s="110" t="inlineStr">
         <is>
-          <t>אופיר חנון בניה ופיקוח</t>
+          <t>נטליה הודיה</t>
         </is>
       </c>
       <c r="B36" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40094 - עובדים אוגוסט</t>
+          <t>מזומן / נחשון</t>
         </is>
       </c>
       <c r="C36" s="111" t="n">
-        <v>8425</v>
+        <v>15803.8</v>
       </c>
       <c r="D36" s="112" t="inlineStr">
         <is>
-          <t>⏳ התקבלו 25,000 ₪ ב-25/09/2026 + 80,000 ₪ ב-06/10/2026 - נותרו 8,425 ₪</t>
+          <t>⏳ שולמו עד כה 7,000 ₪ במזומן: 4,000 ₪ + 3,000 ₪ ביום שלישי 08/09/2026. 💵 המזומן לא נכנס לבנק ולכן אינו ביתרת הבנק. ⚠️ לאימות: ה-4,000 נרשמו בדוח שהיה "נכון ל-09/09" - יש לוודא שזה תשלום נפרד מה-3,000 של 08/09 ולא כפילות. ממשיך בתשלומים שבועיים עד לסגירת היתרה</t>
         </is>
       </c>
       <c r="E36" s="109" t="n"/>
@@ -18529,32 +18564,36 @@
       </c>
       <c r="B37" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40089 - עובדים אוגוסט</t>
+          <t>עמלות ניכיון צ׳קים באופל בלאנס - לחיוב הלקוח</t>
         </is>
       </c>
       <c r="C37" s="111" t="n">
-        <v>91496</v>
-      </c>
-      <c r="D37" s="112" t="n"/>
+        <v>2367</v>
+      </c>
+      <c r="D37" s="112" t="inlineStr">
+        <is>
+          <t>עמלת ניכיון 1,458 (צ׳ק 14291, קבלה 1857 מ-22/07) + עמלת ניכיון 909 (צ׳קים 14297+14298, קבלה 1969 מ-23/08) = 2,367</t>
+        </is>
+      </c>
       <c r="E37" s="109" t="n"/>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="131">
       <c r="A38" s="110" t="inlineStr">
         <is>
-          <t>רמא</t>
+          <t>אופיר חנון בניה ופיקוח</t>
         </is>
       </c>
       <c r="B38" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40112 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40094 - עובדים אוגוסט</t>
         </is>
       </c>
       <c r="C38" s="111" t="n">
-        <v>112041</v>
+        <v>8425</v>
       </c>
       <c r="D38" s="112" t="inlineStr">
         <is>
-          <t>⏳ הופק 05/10/2026</t>
+          <t>⏳ התקבלו 25,000 ₪ ב-25/09/2026 + 80,000 ₪ ב-06/10/2026 - נותרו 8,425 ₪</t>
         </is>
       </c>
       <c r="E38" s="109" t="n"/>
@@ -18562,41 +18601,37 @@
     <row r="39" ht="14.25" customHeight="1" s="131">
       <c r="A39" s="110" t="inlineStr">
         <is>
-          <t>גרייטדור</t>
+          <t>מצודת השלום</t>
         </is>
       </c>
       <c r="B39" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40113 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40089 - עובדים אוגוסט</t>
         </is>
       </c>
       <c r="C39" s="111" t="n">
-        <v>120397</v>
-      </c>
-      <c r="D39" s="112" t="inlineStr">
-        <is>
-          <t>⏳ התקבלו 20,000 ₪ ב-12/10 + 6,513 ₪ ב-13/10/2026 (סה"כ 26,513) - נותרו 120,397 ₪</t>
-        </is>
-      </c>
+        <v>91496</v>
+      </c>
+      <c r="D39" s="112" t="n"/>
       <c r="E39" s="109" t="n"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="131">
       <c r="A40" s="110" t="inlineStr">
         <is>
-          <t>אביאלי אלומיניום</t>
+          <t>רמא</t>
         </is>
       </c>
       <c r="B40" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40117 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40112 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C40" s="111" t="n">
-        <v>0</v>
+        <v>112041</v>
       </c>
       <c r="D40" s="112" t="inlineStr">
         <is>
-          <t>✅ שולם במלואו 12/10/2026 - 15,741 ₪ (העברה מאלי שי בן-חיים). הסכום הנכון לפי שמואל 14/10</t>
+          <t>⏳ הופק 05/10/2026</t>
         </is>
       </c>
       <c r="E40" s="109" t="n"/>
@@ -18604,20 +18639,20 @@
     <row r="41" ht="14.25" customHeight="1" s="131">
       <c r="A41" s="110" t="inlineStr">
         <is>
-          <t>מצודת השלום</t>
+          <t>גרייטדור</t>
         </is>
       </c>
       <c r="B41" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40118 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40113 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C41" s="111" t="n">
-        <v>55833</v>
+        <v>120397</v>
       </c>
       <c r="D41" s="112" t="inlineStr">
         <is>
-          <t>⏳ הופק 05/10/2026</t>
+          <t>⏳ התקבלו 20,000 ₪ ב-12/10 + 6,513 ₪ ב-13/10/2026 (סה"כ 26,513) - נותרו 120,397 ₪</t>
         </is>
       </c>
       <c r="E41" s="109" t="n"/>
@@ -18625,12 +18660,12 @@
     <row r="42" ht="14.25" customHeight="1" s="131">
       <c r="A42" s="110" t="inlineStr">
         <is>
-          <t>ברגשטיין (בי אנד גי)</t>
+          <t>אביאלי אלומיניום</t>
         </is>
       </c>
       <c r="B42" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40119 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40117 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C42" s="111" t="n">
@@ -18638,7 +18673,7 @@
       </c>
       <c r="D42" s="112" t="inlineStr">
         <is>
-          <t>✅ שולם 13/10/2026 - 156,403 ₪ במלואו (העברה מבנק מזרחי)</t>
+          <t>✅ שולם במלואו 12/10/2026 - 15,741 ₪ (העברה מאלי שי בן-חיים). הסכום הנכון לפי שמואל 14/10</t>
         </is>
       </c>
       <c r="E42" s="109" t="n"/>
@@ -18646,16 +18681,16 @@
     <row r="43" ht="14.25" customHeight="1" s="131">
       <c r="A43" s="110" t="inlineStr">
         <is>
-          <t>אופיר חנון בניה ופיקוח</t>
+          <t>מצודת השלום</t>
         </is>
       </c>
       <c r="B43" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40120 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40118 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C43" s="111" t="n">
-        <v>66573</v>
+        <v>55833</v>
       </c>
       <c r="D43" s="112" t="inlineStr">
         <is>
@@ -18667,12 +18702,12 @@
     <row r="44" ht="14.25" customHeight="1" s="131">
       <c r="A44" s="110" t="inlineStr">
         <is>
-          <t>ש.ח.ן כרמלי</t>
+          <t>ברגשטיין (בי אנד גי)</t>
         </is>
       </c>
       <c r="B44" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40121 - עובדים ספטמבר</t>
+          <t>חשבון עסקה 40119 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C44" s="111" t="n">
@@ -18680,7 +18715,7 @@
       </c>
       <c r="D44" s="112" t="inlineStr">
         <is>
-          <t>✅ שולם 08/10/2026 - 77,278 ₪ (חשבונית מס 50377; 47 ₪ יותר מחשבון העסקה 77,231)</t>
+          <t>✅ שולם 13/10/2026 - 156,403 ₪ במלואו (העברה מבנק מזרחי)</t>
         </is>
       </c>
       <c r="E44" s="109" t="n"/>
@@ -18688,20 +18723,20 @@
     <row r="45" ht="14.25" customHeight="1" s="131">
       <c r="A45" s="110" t="inlineStr">
         <is>
-          <t>שבט בנימין</t>
+          <t>אופיר חנון בניה ופיקוח</t>
         </is>
       </c>
       <c r="B45" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40109 - תאגיד השידור</t>
+          <t>חשבון עסקה 40120 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C45" s="111" t="n">
-        <v>7723</v>
+        <v>66573</v>
       </c>
       <c r="D45" s="112" t="inlineStr">
         <is>
-          <t>⏳ הופק 22/09/2026. חשבונית מס 50373 הופקה עליו 05/10 (אותו סכום - לא לספור פעמיים)</t>
+          <t>⏳ הופק 05/10/2026</t>
         </is>
       </c>
       <c r="E45" s="109" t="n"/>
@@ -18709,20 +18744,20 @@
     <row r="46" ht="14.25" customHeight="1" s="131">
       <c r="A46" s="110" t="inlineStr">
         <is>
-          <t>שבט בנימין</t>
+          <t>ש.ח.ן כרמלי</t>
         </is>
       </c>
       <c r="B46" s="110" t="inlineStr">
         <is>
-          <t>חשבון עסקה 40110 - עובדים אסף ספטמבר</t>
+          <t>חשבון עסקה 40121 - עובדים ספטמבר</t>
         </is>
       </c>
       <c r="C46" s="111" t="n">
-        <v>19171</v>
+        <v>0</v>
       </c>
       <c r="D46" s="112" t="inlineStr">
         <is>
-          <t>⏳ הופק 22/09/2026</t>
+          <t>✅ שולם 08/10/2026 - 77,278 ₪ (חשבונית מס 50377; 47 ₪ יותר מחשבון העסקה 77,231)</t>
         </is>
       </c>
       <c r="E46" s="109" t="n"/>
@@ -18730,222 +18765,262 @@
     <row r="47" ht="14.25" customHeight="1" s="131">
       <c r="A47" s="110" t="inlineStr">
         <is>
+          <t>שבט בנימין</t>
+        </is>
+      </c>
+      <c r="B47" s="110" t="inlineStr">
+        <is>
+          <t>חשבון עסקה 40109 - תאגיד השידור</t>
+        </is>
+      </c>
+      <c r="C47" s="111" t="n">
+        <v>7723</v>
+      </c>
+      <c r="D47" s="112" t="inlineStr">
+        <is>
+          <t>⏳ הופק 22/09/2026. חשבונית מס 50373 הופקה עליו 05/10 (אותו סכום - לא לספור פעמיים)</t>
+        </is>
+      </c>
+      <c r="E47" s="109" t="n"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" s="131">
+      <c r="A48" s="110" t="inlineStr">
+        <is>
+          <t>שבט בנימין</t>
+        </is>
+      </c>
+      <c r="B48" s="110" t="inlineStr">
+        <is>
+          <t>חשבון עסקה 40110 - עובדים אסף ספטמבר</t>
+        </is>
+      </c>
+      <c r="C48" s="111" t="n">
+        <v>19171</v>
+      </c>
+      <c r="D48" s="112" t="inlineStr">
+        <is>
+          <t>⏳ הופק 22/09/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="109" t="n"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1" s="131">
+      <c r="A49" s="110" t="inlineStr">
+        <is>
           <t>איבריקה אינטרנשיונל</t>
         </is>
       </c>
-      <c r="B47" s="110" t="inlineStr">
+      <c r="B49" s="110" t="inlineStr">
         <is>
           <t>שכירות דירות (אשקלון, אסירי ציון, מיטות קארו 7) - אוקטובר</t>
         </is>
       </c>
-      <c r="C47" s="111" t="n">
+      <c r="C49" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="112" t="inlineStr">
+      <c r="D49" s="112" t="inlineStr">
         <is>
           <t>✅ שולם 11/10/2026 - 13,570 ₪ כולל מע"מ (העברה מבנק הפועלים)</t>
         </is>
       </c>
-      <c r="E47" s="109" t="n"/>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="131">
-      <c r="A48" s="113" t="inlineStr">
+      <c r="E49" s="109" t="n"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" s="131">
+      <c r="A50" s="113" t="inlineStr">
         <is>
           <t>סה"כ לקוחות חייבים לנו</t>
         </is>
       </c>
-      <c r="B48" s="114" t="n"/>
-      <c r="C48" s="115">
-        <f>SUM(C34:C47)</f>
-        <v/>
-      </c>
-      <c r="D48" s="116" t="n"/>
-      <c r="E48" s="109" t="n"/>
-    </row>
-    <row r="49" ht="14.25" customHeight="1" s="131"/>
-    <row r="50" ht="14.25" customHeight="1" s="131">
-      <c r="A50" s="78" t="inlineStr">
+      <c r="B50" s="114" t="n"/>
+      <c r="C50" s="115">
+        <f>SUM(C36:C49)</f>
+        <v/>
+      </c>
+      <c r="D50" s="116" t="n"/>
+      <c r="E50" s="109" t="n"/>
+    </row>
+    <row r="51" ht="14.25" customHeight="1" s="131"/>
+    <row r="52" ht="14.25" customHeight="1" s="131">
+      <c r="A52" s="78" t="inlineStr">
         <is>
           <t>📊  סיכום - כמה צריך כדי לסגור הכל</t>
         </is>
       </c>
-      <c r="B50" s="78" t="n"/>
-      <c r="C50" s="78" t="n"/>
-      <c r="D50" s="78" t="n"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1" s="131">
-      <c r="A51" s="58" t="inlineStr">
+      <c r="B52" s="78" t="n"/>
+      <c r="C52" s="78" t="n"/>
+      <c r="D52" s="78" t="n"/>
+    </row>
+    <row r="53" ht="14.25" customHeight="1" s="131">
+      <c r="A53" s="58" t="inlineStr">
         <is>
           <t>יתרה בבנק (14/10/2026) - כולל ברגשטיין 156,403, גרייטדור 26,513, אביאלי 15,741, אחרי צ׳ק ש. מינסקי יזמות 16,520</t>
         </is>
       </c>
-      <c r="C51" s="82" t="n">
+      <c r="C53" s="82" t="n">
         <v>251008.45</v>
       </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1" s="131">
-      <c r="A52" s="58" t="inlineStr">
-        <is>
-          <t>+ לקוחות חייבים לנו (צפוי להיכנס)</t>
-        </is>
-      </c>
-      <c r="C52" s="82">
-        <f>C48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1" s="131">
-      <c r="A53" s="117" t="inlineStr">
-        <is>
-          <t>סה"כ משאבים זמינים (בנק + לקוחות)</t>
-        </is>
-      </c>
-      <c r="B53" s="117" t="n"/>
-      <c r="C53" s="118">
-        <f>C51+C52</f>
-        <v/>
-      </c>
-      <c r="D53" s="117" t="n"/>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="131">
       <c r="A54" s="58" t="inlineStr">
         <is>
+          <t>+ לקוחות חייבים לנו (צפוי להיכנס)</t>
+        </is>
+      </c>
+      <c r="C54" s="82">
+        <f>C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1" s="131">
+      <c r="A55" s="117" t="inlineStr">
+        <is>
+          <t>סה"כ משאבים זמינים (בנק + לקוחות)</t>
+        </is>
+      </c>
+      <c r="B55" s="117" t="n"/>
+      <c r="C55" s="118">
+        <f>C53+C54</f>
+        <v/>
+      </c>
+      <c r="D55" s="117" t="n"/>
+    </row>
+    <row r="56" ht="14.25" customHeight="1" s="131">
+      <c r="A56" s="58" t="inlineStr">
+        <is>
           <t>− סה״כ ממתין לתשלום (תאגידי אוגוסט: יתרת פאנג אחרי 230,000 ב-07/10) - לא כולל צ׳ק פאנג יוני השני (125,000 ב-25/10) ו-ISRAEL CARGO (19,770 ב-10/10)</t>
         </is>
       </c>
-      <c r="C54" s="82">
-        <f>D28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1" s="131">
-      <c r="A55" s="119" t="inlineStr">
+      <c r="C56" s="82">
+        <f>D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="14.25" customHeight="1" s="131">
+      <c r="A57" s="119" t="inlineStr">
         <is>
           <t>✅  עודף אחרי כל התשלומים</t>
         </is>
       </c>
-      <c r="B55" s="119" t="n"/>
-      <c r="C55" s="120">
-        <f>C53-C54</f>
-        <v/>
-      </c>
-      <c r="D55" s="119" t="n"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1" s="131"/>
-    <row r="57" ht="14.25" customHeight="1" s="131">
-      <c r="A57" s="78" t="inlineStr">
+      <c r="B57" s="119" t="n"/>
+      <c r="C57" s="120">
+        <f>C55-C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="119" t="n"/>
+    </row>
+    <row r="58" ht="14.25" customHeight="1" s="131"/>
+    <row r="59" ht="14.25" customHeight="1" s="131">
+      <c r="A59" s="78" t="inlineStr">
         <is>
           <t>🏦  גמל - קופות גמל (מגדל + מנורה)</t>
         </is>
       </c>
-      <c r="B57" s="78" t="n"/>
-      <c r="C57" s="78" t="n"/>
-      <c r="D57" s="78" t="n"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1" s="131">
-      <c r="A58" s="121" t="inlineStr">
-        <is>
-          <t>עובד</t>
-        </is>
-      </c>
-      <c r="B58" s="121" t="inlineStr">
-        <is>
-          <t>קופה</t>
-        </is>
-      </c>
-      <c r="C58" s="121" t="inlineStr">
-        <is>
-          <t>יוני (₪)</t>
-        </is>
-      </c>
-      <c r="D58" s="121" t="inlineStr">
-        <is>
-          <t>יולי (₪)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1" s="131">
-      <c r="A59" s="122" t="inlineStr">
-        <is>
-          <t>קארו עדאלה</t>
-        </is>
-      </c>
-      <c r="B59" s="121" t="inlineStr">
-        <is>
-          <t>מגדל</t>
-        </is>
-      </c>
-      <c r="C59" s="123" t="n">
-        <v>2273</v>
-      </c>
-      <c r="D59" s="123" t="n">
-        <v>2140</v>
-      </c>
+      <c r="B59" s="78" t="n"/>
+      <c r="C59" s="78" t="n"/>
+      <c r="D59" s="78" t="n"/>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="131">
       <c r="A60" s="121" t="inlineStr">
         <is>
+          <t>עובד</t>
+        </is>
+      </c>
+      <c r="B60" s="121" t="inlineStr">
+        <is>
+          <t>קופה</t>
+        </is>
+      </c>
+      <c r="C60" s="121" t="inlineStr">
+        <is>
+          <t>יוני (₪)</t>
+        </is>
+      </c>
+      <c r="D60" s="121" t="inlineStr">
+        <is>
+          <t>יולי (₪)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1" s="131">
+      <c r="A61" s="122" t="inlineStr">
+        <is>
+          <t>קארו עדאלה</t>
+        </is>
+      </c>
+      <c r="B61" s="121" t="inlineStr">
+        <is>
+          <t>מגדל</t>
+        </is>
+      </c>
+      <c r="C61" s="123" t="n">
+        <v>2273</v>
+      </c>
+      <c r="D61" s="123" t="n">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" customHeight="1" s="131">
+      <c r="A62" s="121" t="inlineStr">
+        <is>
           <t>יואייב נחשון חי</t>
         </is>
       </c>
-      <c r="B60" s="121" t="inlineStr">
+      <c r="B62" s="121" t="inlineStr">
         <is>
           <t>מנורה</t>
         </is>
       </c>
-      <c r="C60" s="123" t="n">
+      <c r="C62" s="123" t="n">
         <v>1184</v>
       </c>
-      <c r="D60" s="123" t="n">
+      <c r="D62" s="123" t="n">
         <v>1202</v>
       </c>
     </row>
-    <row r="61" ht="14.25" customHeight="1" s="131">
-      <c r="A61" s="121" t="inlineStr">
+    <row r="63" ht="14.25" customHeight="1" s="131">
+      <c r="A63" s="121" t="inlineStr">
         <is>
           <t>מינסקי שלומי</t>
         </is>
       </c>
-      <c r="B61" s="121" t="inlineStr">
+      <c r="B63" s="121" t="inlineStr">
         <is>
           <t>מנורה</t>
         </is>
       </c>
-      <c r="C61" s="123" t="n">
+      <c r="C63" s="123" t="n">
         <v>2248</v>
       </c>
-      <c r="D61" s="123" t="n">
+      <c r="D63" s="123" t="n">
         <v>3552</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1" s="131">
-      <c r="A62" s="117" t="inlineStr">
+    <row r="64" ht="14.25" customHeight="1" s="131">
+      <c r="A64" s="117" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B62" s="117" t="n"/>
-      <c r="C62" s="118" t="n">
+      <c r="B64" s="117" t="n"/>
+      <c r="C64" s="118" t="n">
         <v>5705</v>
       </c>
-      <c r="D62" s="118" t="n">
+      <c r="D64" s="118" t="n">
         <v>6894</v>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1" s="131">
-      <c r="A63" s="117" t="inlineStr">
+    <row r="65" ht="14.25" customHeight="1" s="131">
+      <c r="A65" s="117" t="inlineStr">
         <is>
           <t>סה"כ גמל (יוני+יולי)</t>
         </is>
       </c>
-      <c r="B63" s="117" t="n"/>
-      <c r="C63" s="118" t="n"/>
-      <c r="D63" s="118" t="n">
+      <c r="B65" s="117" t="n"/>
+      <c r="C65" s="118" t="n"/>
+      <c r="D65" s="118" t="n">
         <v>12599</v>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1" s="131"/>
-    <row r="65" ht="14.25" customHeight="1" s="131"/>
     <row r="66" ht="14.25" customHeight="1" s="131"/>
     <row r="67" ht="14.25" customHeight="1" s="131"/>
     <row r="68" ht="14.25" customHeight="1" s="131"/>
@@ -19886,12 +19961,12 @@
     <row r="1003" ht="14.25" customHeight="1" s="131"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -4163,8 +4163,8 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="A4:G4"/>
@@ -15097,7 +15097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="131" min="1" max="1"/>
@@ -16591,7 +16591,7 @@
     <row r="50" ht="60" customHeight="1" s="131">
       <c r="A50" s="141" t="inlineStr">
         <is>
-          <t>הערה: הנתונים עד 14/10/2026 מאומתים מול דוח בנק לאומי (251,008.45 ₪, דוח 14/10/2026). ב-11/10 נכנסו איבריקה 13,570 (שכירות אוקטובר) ואחים לימור 15,340 + 29,500 (שכירות בית צפאפא + קורצאק); יצאו ארנונה 6,974.85 (6 חיובים), 3 משכורות 24,515, הפקדה לחיסכון 20,000 והעברה עצמית 20,000. ב-12/10 יצאו שכירויות בית צפאפא 8,850 וקורצאק 12,980. ✅ פאנג אוגוסט: 230,000 ירדו 07/10 - נותרו 208,316.30 ב-3 צ׳קים. ⏳ ISRAEL CARGO LOG 19,770 ₪ (תשלום 1 מתוך 8) - ההעברה ממתינה לחתימות, טרם ירדה בבנק נכון ל-14/10. ב-12/10 נכנסו גם אביאלי (אלי שי בן-חיים) 15,741 וגרייטדור 20,000. ב-13/10 נכנסו ברגשטיין 156,403 (40119 במלואו) וגרייטדור 6,513; ירד צ׳ק 5000289 לש. מינסקי יזמות 16,520. ב-14/10 פרעון פקדון 45,605.38 קוזז באותו יום (נטו 0, תנועות היום טרם סופיות).</t>
+          <t>הערה: הנתונים עד 14/10/2026 מאומתים מול דוח בנק לאומי (251,008.45 ₪, דוח 14/10/2026). ב-11/10 נכנסו איבריקה 13,570 (שכירות אוקטובר) ואחים לימור 15,340 + 29,500 (שכירות בית צפאפא + קורצאק); יצאו ארנונה 6,974.85 (6 חיובים), 3 משכורות 24,515, הפקדה לחיסכון 20,000 והעברה עצמית 20,000. ב-12/10 יצאו שכירויות בית צפאפא 8,850 וקורצאק 12,980. ✅ פאנג אוגוסט: 230,000 ירדו 07/10 - נותרו 208,316.30 ב-3 צ׳קים. ⏳ ISRAEL CARGO LOG 19,770 ₪ (תשלום 1 מתוך 8) - ההעברה ממתינה לחתימות, טרם ירדה בבנק נכון ל-14/10. ב-12/10 נכנסו גם אביאלי (אלי שי בן-חיים) 15,741 וגרייטדור 20,000. ב-13/10 נכנסו ברגשטיין 156,403 (40119 במלואו) וגרייטדור 6,513; ירד צ׳ק 5000289 לש. מינסקי יזמות 16,520. ב-14/10 פרעון פקדון 45,605.38 קוזז באותו יום (נטו 0, תנועות היום טרם סופיות). ⏳ 14/10: שכירויות דירות העובדים 28,300 (תומא וסאם, שישא גבריאל, רחל מסטשי, טייטלבוים, זלץ) הועברו וממתינות לחתימות.</t>
         </is>
       </c>
     </row>
@@ -16738,16 +16738,16 @@
     </row>
     <row r="60" ht="14.25" customHeight="1" s="131">
       <c r="A60" s="95" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B60" s="96" t="inlineStr">
         <is>
-          <t>לאומי מאסטרקרד</t>
+          <t>תומא וסאם - שכירות בית חנינא</t>
         </is>
       </c>
       <c r="C60" s="97" t="n"/>
       <c r="D60" s="98" t="n">
-        <v>5694.18</v>
+        <v>9600</v>
       </c>
       <c r="E60" s="100">
         <f>E59+N(C60)-N(D60)</f>
@@ -16755,7 +16755,7 @@
       </c>
       <c r="F60" s="101" t="inlineStr">
         <is>
-          <t>חיוב כרטיס (לפי הבנק)</t>
+          <t>קבועה · ⏳ ההעברה בוצעה 14/10 וממתינה לחתימות (לפי שמואל)</t>
         </is>
       </c>
       <c r="G60" s="102" t="inlineStr">
@@ -16771,16 +16771,16 @@
     </row>
     <row r="61" ht="14.25" customHeight="1" s="131">
       <c r="A61" s="95" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B61" s="96" t="inlineStr">
         <is>
-          <t>דיינרס</t>
+          <t>שישא גבריאל - שכירות קארו 7</t>
         </is>
       </c>
       <c r="C61" s="97" t="n"/>
       <c r="D61" s="98" t="n">
-        <v>171</v>
+        <v>7000</v>
       </c>
       <c r="E61" s="100">
         <f>E60+N(C61)-N(D61)</f>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="F61" s="101" t="inlineStr">
         <is>
-          <t>חיוב כרטיס (לפי הבנק)</t>
+          <t>קבועה · ⏳ ההעברה בוצעה 14/10 וממתינה לחתימות (לפי שמואל)</t>
         </is>
       </c>
       <c r="G61" s="102" t="inlineStr">
@@ -16804,16 +16804,16 @@
     </row>
     <row r="62" ht="14.25" customHeight="1" s="131">
       <c r="A62" s="95" t="n">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="B62" s="96" t="inlineStr">
         <is>
-          <t>פרעון הלוואה</t>
+          <t>רחל מסטשי - שכירות אסירי ציון</t>
         </is>
       </c>
       <c r="C62" s="97" t="n"/>
       <c r="D62" s="98" t="n">
-        <v>4044.58</v>
+        <v>4700</v>
       </c>
       <c r="E62" s="100">
         <f>E61+N(C62)-N(D62)</f>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="F62" s="101" t="inlineStr">
         <is>
-          <t>לפי הבנק</t>
+          <t>קבועה · ⏳ ההעברה בוצעה 14/10 וממתינה לחתימות (לפי שמואל)</t>
         </is>
       </c>
       <c r="G62" s="102" t="inlineStr">
@@ -16837,16 +16837,16 @@
     </row>
     <row r="63" ht="14.25" customHeight="1" s="131">
       <c r="A63" s="95" t="n">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="B63" s="96" t="inlineStr">
         <is>
-          <t>פרעון שיק</t>
+          <t>הינדי טייטלבוים - שכירות קארו 3</t>
         </is>
       </c>
       <c r="C63" s="97" t="n"/>
       <c r="D63" s="98" t="n">
-        <v>1825</v>
+        <v>4000</v>
       </c>
       <c r="E63" s="100">
         <f>E62+N(C63)-N(D63)</f>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="F63" s="101" t="inlineStr">
         <is>
-          <t>לפי הבנק</t>
+          <t>קבועה · ⏳ ההעברה בוצעה 14/10 וממתינה לחתימות (לפי שמואל)</t>
         </is>
       </c>
       <c r="G63" s="102" t="inlineStr">
@@ -16870,16 +16870,16 @@
     </row>
     <row r="64" ht="14.25" customHeight="1" s="131">
       <c r="A64" s="95" t="n">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="B64" s="96" t="inlineStr">
         <is>
-          <t>ד.יוחאי - חשבונית ספטמבר IN264000117</t>
+          <t>זאב זלץ - שכירות קארו 11</t>
         </is>
       </c>
       <c r="C64" s="97" t="n"/>
       <c r="D64" s="98" t="n">
-        <v>35432.57</v>
+        <v>3000</v>
       </c>
       <c r="E64" s="100">
         <f>E63+N(C64)-N(D64)</f>
@@ -16887,32 +16887,32 @@
       </c>
       <c r="F64" s="101" t="inlineStr">
         <is>
-          <t>עובדים זרים ספטמבר · 417.05 שעות × 72 ₪ + מע"מ · מועד תשלום יוחאי: ה-20 לחודש</t>
+          <t>קבועה · ⏳ ההעברה בוצעה 14/10 וממתינה לחתימות (לפי שמואל)</t>
         </is>
       </c>
       <c r="G64" s="102" t="inlineStr">
         <is>
-          <t>📤 הוצאה</t>
+          <t>🔁 קבוע</t>
         </is>
       </c>
       <c r="H64" s="104" t="inlineStr">
         <is>
-          <t>לא</t>
+          <t>כן</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="131">
       <c r="A65" s="95" t="n">
-        <v>46320</v>
+        <v>46310</v>
       </c>
       <c r="B65" s="96" t="inlineStr">
         <is>
-          <t>פוגין אינטרנשיונל - חשבונית ספטמבר 01/000938</t>
+          <t>לאומי מאסטרקרד</t>
         </is>
       </c>
       <c r="C65" s="97" t="n"/>
       <c r="D65" s="98" t="n">
-        <v>18262.9</v>
+        <v>5694.18</v>
       </c>
       <c r="E65" s="100">
         <f>E64+N(C65)-N(D65)</f>
@@ -16920,32 +16920,32 @@
       </c>
       <c r="F65" s="101" t="inlineStr">
         <is>
-          <t>עובדים אוזביקים ספטמבר · 15,477 + מע"מ · מועד תשלום פוגין: ה-25 לחודש</t>
+          <t>חיוב כרטיס (לפי הבנק)</t>
         </is>
       </c>
       <c r="G65" s="102" t="inlineStr">
         <is>
-          <t>📤 הוצאה</t>
+          <t>🔁 קבוע</t>
         </is>
       </c>
       <c r="H65" s="104" t="inlineStr">
         <is>
-          <t>לא</t>
+          <t>כן</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="131">
       <c r="A66" s="95" t="n">
-        <v>46320</v>
+        <v>46310</v>
       </c>
       <c r="B66" s="96" t="inlineStr">
         <is>
-          <t>שי-לי כח אדם - חשבונית ספטמבר 230747</t>
+          <t>דיינרס</t>
         </is>
       </c>
       <c r="C66" s="97" t="n"/>
       <c r="D66" s="98" t="n">
-        <v>44571</v>
+        <v>171</v>
       </c>
       <c r="E66" s="100">
         <f>E65+N(C66)-N(D66)</f>
@@ -16953,32 +16953,32 @@
       </c>
       <c r="F66" s="101" t="inlineStr">
         <is>
-          <t>532 שעות × 71 ₪ + מע"מ · אתר הקליר, ירושלים · מועד תשלום שי-לי: ה-25 לחודש</t>
+          <t>חיוב כרטיס (לפי הבנק)</t>
         </is>
       </c>
       <c r="G66" s="102" t="inlineStr">
         <is>
-          <t>📤 הוצאה</t>
+          <t>🔁 קבוע</t>
         </is>
       </c>
       <c r="H66" s="104" t="inlineStr">
         <is>
-          <t>לא</t>
+          <t>כן</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1" s="131">
       <c r="A67" s="95" t="n">
-        <v>46320</v>
+        <v>46315</v>
       </c>
       <c r="B67" s="96" t="inlineStr">
         <is>
-          <t>פאנג שירותי כח אדם - צ׳ק 5000346 (חשבונית יוני 01/002663)</t>
+          <t>פרעון הלוואה</t>
         </is>
       </c>
       <c r="C67" s="97" t="n"/>
       <c r="D67" s="98" t="n">
-        <v>125000</v>
+        <v>4044.58</v>
       </c>
       <c r="E67" s="100">
         <f>E66+N(C67)-N(D67)</f>
@@ -16986,38 +16986,198 @@
       </c>
       <c r="F67" s="101" t="inlineStr">
         <is>
+          <t>לפי הבנק</t>
+        </is>
+      </c>
+      <c r="G67" s="102" t="inlineStr">
+        <is>
+          <t>🔁 קבוע</t>
+        </is>
+      </c>
+      <c r="H67" s="104" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14.25" customHeight="1" s="131">
+      <c r="A68" s="95" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B68" s="96" t="inlineStr">
+        <is>
+          <t>פרעון שיק</t>
+        </is>
+      </c>
+      <c r="C68" s="97" t="n"/>
+      <c r="D68" s="98" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E68" s="100">
+        <f>E67+N(C68)-N(D68)</f>
+        <v/>
+      </c>
+      <c r="F68" s="101" t="inlineStr">
+        <is>
+          <t>לפי הבנק</t>
+        </is>
+      </c>
+      <c r="G68" s="102" t="inlineStr">
+        <is>
+          <t>🔁 קבוע</t>
+        </is>
+      </c>
+      <c r="H68" s="104" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="14.25" customHeight="1" s="131">
+      <c r="A69" s="95" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B69" s="96" t="inlineStr">
+        <is>
+          <t>ד.יוחאי - חשבונית ספטמבר IN264000117</t>
+        </is>
+      </c>
+      <c r="C69" s="97" t="n"/>
+      <c r="D69" s="98" t="n">
+        <v>35432.57</v>
+      </c>
+      <c r="E69" s="100">
+        <f>E68+N(C69)-N(D69)</f>
+        <v/>
+      </c>
+      <c r="F69" s="101" t="inlineStr">
+        <is>
+          <t>עובדים זרים ספטמבר · 417.05 שעות × 72 ₪ + מע"מ · מועד תשלום יוחאי: ה-20 לחודש</t>
+        </is>
+      </c>
+      <c r="G69" s="102" t="inlineStr">
+        <is>
+          <t>📤 הוצאה</t>
+        </is>
+      </c>
+      <c r="H69" s="104" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="14.25" customHeight="1" s="131">
+      <c r="A70" s="95" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="96" t="inlineStr">
+        <is>
+          <t>פוגין אינטרנשיונל - חשבונית ספטמבר 01/000938</t>
+        </is>
+      </c>
+      <c r="C70" s="97" t="n"/>
+      <c r="D70" s="98" t="n">
+        <v>18262.9</v>
+      </c>
+      <c r="E70" s="100">
+        <f>E69+N(C70)-N(D70)</f>
+        <v/>
+      </c>
+      <c r="F70" s="101" t="inlineStr">
+        <is>
+          <t>עובדים אוזביקים ספטמבר · 15,477 + מע"מ · מועד תשלום פוגין: ה-25 לחודש</t>
+        </is>
+      </c>
+      <c r="G70" s="102" t="inlineStr">
+        <is>
+          <t>📤 הוצאה</t>
+        </is>
+      </c>
+      <c r="H70" s="104" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="14.25" customHeight="1" s="131">
+      <c r="A71" s="95" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B71" s="96" t="inlineStr">
+        <is>
+          <t>שי-לי כח אדם - חשבונית ספטמבר 230747</t>
+        </is>
+      </c>
+      <c r="C71" s="97" t="n"/>
+      <c r="D71" s="98" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E71" s="100">
+        <f>E70+N(C71)-N(D71)</f>
+        <v/>
+      </c>
+      <c r="F71" s="101" t="inlineStr">
+        <is>
+          <t>532 שעות × 71 ₪ + מע"מ · אתר הקליר, ירושלים · מועד תשלום שי-לי: ה-25 לחודש</t>
+        </is>
+      </c>
+      <c r="G71" s="102" t="inlineStr">
+        <is>
+          <t>📤 הוצאה</t>
+        </is>
+      </c>
+      <c r="H71" s="104" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14.25" customHeight="1" s="131">
+      <c r="A72" s="95" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B72" s="96" t="inlineStr">
+        <is>
+          <t>פאנג שירותי כח אדם - צ׳ק 5000346 (חשבונית יוני 01/002663)</t>
+        </is>
+      </c>
+      <c r="C72" s="97" t="n"/>
+      <c r="D72" s="98" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E72" s="100">
+        <f>E71+N(C72)-N(D72)</f>
+        <v/>
+      </c>
+      <c r="F72" s="101" t="inlineStr">
+        <is>
           <t>צ׳ק דחוי שני ואחרון לחשבונית יוני</t>
         </is>
       </c>
-      <c r="G67" s="102" t="inlineStr">
+      <c r="G72" s="102" t="inlineStr">
         <is>
           <t>📤 הוצאה</t>
         </is>
       </c>
-      <c r="H67" s="104" t="inlineStr">
+      <c r="H72" s="104" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1" s="131">
-      <c r="A68" s="58" t="inlineStr">
+    <row r="73" ht="14.25" customHeight="1" s="131">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>יתרה צפויה בסוף אוקטובר (אחרי 230,000 לפאנג אוגוסט, ללא שכירויות/משכורות שטרם נרשמו וללא תקבולי לקוחות - ראה "ממתינים לתשלום")</t>
         </is>
       </c>
-      <c r="C68" s="82" t="n"/>
-      <c r="D68" s="82" t="n"/>
-      <c r="E68" s="84">
-        <f>E67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="14.25" customHeight="1" s="131"/>
-    <row r="70" ht="14.25" customHeight="1" s="131"/>
-    <row r="71" ht="14.25" customHeight="1" s="131"/>
-    <row r="72" ht="14.25" customHeight="1" s="131"/>
-    <row r="73" ht="14.25" customHeight="1" s="131"/>
+      <c r="C73" s="82" t="n"/>
+      <c r="D73" s="82" t="n"/>
+      <c r="E73" s="84">
+        <f>E72</f>
+        <v/>
+      </c>
+    </row>
     <row r="74" ht="14.25" customHeight="1" s="131"/>
     <row r="75" ht="14.25" customHeight="1" s="131"/>
     <row r="76" ht="14.25" customHeight="1" s="131"/>
@@ -19961,12 +20121,12 @@
     <row r="1003" ht="14.25" customHeight="1" s="131"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="693">
   <si>
     <t xml:space="preserve">חוב לתאגידי כוח אדם  |  ישר שירותי קרקע לקבלן ולפועל בע"מ  |  ינואר–ספטמבר 2026</t>
   </si>
@@ -1725,10 +1725,10 @@
     <t xml:space="preserve">חשבון עסקה 40119 - עובדים ספטמבר, פרויקט הקליר (העברה מבנק מזרחי). ✅ שולם במלואו</t>
   </si>
   <si>
-    <t xml:space="preserve">שיק 5000289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ שיק - לבדוק למי ועבור מה. ייתכן ש. מינסקי יזמות (שולמו 16,520 גם ב-13/07 וב-16/08)</t>
+    <t xml:space="preserve">ש. מינסקי יזמות - שיק 5000289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ זוהה ע"י שמואל 15/10 - תשלום לש. מינסקי יזמות (כולל מע"מ). ברשימת הממתינים נרשם 16,250 - בפועל 16,520</t>
   </si>
   <si>
     <t xml:space="preserve">על חשבון חשבון עסקה 40113 - סה"כ 26,513 ב-12-13/10, נותרו 120,397</t>
@@ -1776,7 +1776,7 @@
     <t xml:space="preserve">יתרה – 15/10/2026 (מאומת מול הבנק: 159,912.27 ₪)</t>
   </si>
   <si>
-    <t xml:space="preserve">הערה: הנתונים עד 15/10/2026 מאומתים מול דוח בנק לאומי (159,912.27 ₪, דוח 15/10/2026; תנועות 15/10 אינן סופיות). ב-12-13/10 נכנסו ברגשטיין 156,403 (40119 נסגר), גרייטדור 26,513 (על חשבון 40113) ואביאלי 15,741; יצא שיק 5000289 16,520 (⚠️ לזהות). ב-14/10 יצאו ISRAEL CARGO 19,770 (תשלום 1/8), ג.ד קלמרה 30,647, שכירויות דירות 28,300, סגירות התחשבנות קבאסה 3,678 וקוט 2,418 ופרידמן 400. פיקדון 45,605 נפדה וקוזז - נטו 0. ב-15/10 חיובי כרטיסים 5,883.18.</t>
+    <t xml:space="preserve">הערה: הנתונים עד 15/10/2026 מאומתים מול דוח בנק לאומי (159,912.27 ₪, דוח 15/10/2026; תנועות 15/10 אינן סופיות). ב-12-13/10 נכנסו ברגשטיין 156,403 (40119 נסגר), גרייטדור 26,513 (על חשבון 40113) ואביאלי 15,741; יצא שיק 5000289 16,520 לש. מינסקי יזמות. ב-14/10 יצאו ISRAEL CARGO 19,770 (תשלום 1/8), ג.ד קלמרה 30,647, שכירויות דירות 28,300, סגירות התחשבנות קבאסה 3,678 וקוט 2,418 ופרידמן 400. פיקדון 45,605 נפדה וקוזז - נטו 0. ב-15/10 חיובי כרטיסים 5,883.18.</t>
   </si>
   <si>
     <t xml:space="preserve">סה"כ הוצאות שכן שייכות לחודש (שכירות, קבועות, כרטיסי אשראי, מסים)</t>
@@ -1905,7 +1905,7 @@
     <t xml:space="preserve">ש. מינסקי יזמות</t>
   </si>
   <si>
-    <t xml:space="preserve">⏳ להעברה (כולל מע"מ) - לפי שמואל, 11/10/2026 · ⚠️ ב-13/10 ירד שיק 5000289 על 16,520 ₪ - ייתכן שזה התשלום (16,520 ולא 16,250?) - לאשר</t>
+    <t xml:space="preserve">✅ שולם 13/10/2026 בשיק 5000289 - 16,520 ₪ (נרשם כאן 16,250; הסכום הנכון 16,520) - אושר ע"י שמואל 15/10</t>
   </si>
   <si>
     <t xml:space="preserve">אחים לימור – חשבון עסקה 8052</t>
@@ -1932,7 +1932,7 @@
     <t xml:space="preserve">סה״כ תזרים אוגוסט + ספטמבר</t>
   </si>
   <si>
-    <t xml:space="preserve">💰  סה״כ ממתין לתשלום (יתרת פאנג אוגוסט + פוגין, שי-לי, אחים לימור ויוחאי ספטמבר + ש. מינסקי יזמות + רז שרי)</t>
+    <t xml:space="preserve">💰  סה״כ ממתין לתשלום (יתרת פאנג אוגוסט + פוגין, שי-לי, אחים לימור ויוחאי ספטמבר + רז שרי)</t>
   </si>
   <si>
     <t xml:space="preserve">💰  לקוחות חייבים לנו</t>
@@ -2458,12 +2458,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2479,135 +2479,139 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2615,19 +2619,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2635,199 +2635,199 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2839,83 +2839,87 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="26" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2923,15 +2927,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="29" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2939,15 +2943,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2955,31 +2959,31 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4451,26 +4455,26 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B66" s="30" t="n">
+      <c r="B66" s="31" t="n">
         <v>2204</v>
       </c>
-      <c r="C66" s="30" t="s">
+      <c r="C66" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D66" s="31" t="n">
+      <c r="D66" s="32" t="n">
         <v>164619.44</v>
       </c>
-      <c r="E66" s="31" t="n">
+      <c r="E66" s="32" t="n">
         <v>144703.45</v>
       </c>
-      <c r="F66" s="31" t="n">
+      <c r="F66" s="32" t="n">
         <f aca="false">D66-E66</f>
         <v>19915.99</v>
       </c>
-      <c r="G66" s="30" t="s">
+      <c r="G66" s="31" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4657,7 +4661,7 @@
       <c r="B75" s="7" t="n">
         <v>230703</v>
       </c>
-      <c r="C75" s="32" t="s">
+      <c r="C75" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D75" s="8" t="n">
@@ -4783,7 +4787,7 @@
       <c r="B81" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C81" s="33" t="n">
+      <c r="C81" s="34" t="n">
         <v>46295</v>
       </c>
       <c r="D81" s="21" t="n">
@@ -4830,18 +4834,18 @@
       <c r="G83" s="20"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B84" s="34"/>
-      <c r="C84" s="34"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="34"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="35"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="37" t="s">
         <v>3</v>
       </c>
       <c r="B85" s="5" t="s">
@@ -4850,13 +4854,13 @@
       <c r="C85" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D85" s="37" t="s">
+      <c r="D85" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E85" s="37" t="s">
+      <c r="E85" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F85" s="37" t="s">
+      <c r="F85" s="38" t="s">
         <v>8</v>
       </c>
       <c r="G85" s="5" t="s">
@@ -4870,7 +4874,7 @@
       <c r="B86" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C86" s="32" t="s">
+      <c r="C86" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D86" s="8" t="n">
@@ -4908,18 +4912,18 @@
       <c r="G87" s="20"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="B88" s="34"/>
-      <c r="C88" s="34"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="34"/>
+      <c r="B88" s="35"/>
+      <c r="C88" s="35"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="35"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="36" t="s">
+      <c r="A89" s="37" t="s">
         <v>3</v>
       </c>
       <c r="B89" s="5" t="s">
@@ -4928,13 +4932,13 @@
       <c r="C89" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D89" s="37" t="s">
+      <c r="D89" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E89" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F89" s="37" t="s">
+      <c r="F89" s="38" t="s">
         <v>8</v>
       </c>
       <c r="G89" s="5" t="s">
@@ -4948,7 +4952,7 @@
       <c r="B90" s="7" t="n">
         <v>20019</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="C90" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D90" s="8" t="n">
@@ -4993,18 +4997,18 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="38" t="s">
+      <c r="A94" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B94" s="38"/>
-      <c r="C94" s="38"/>
-      <c r="D94" s="39" t="n">
+      <c r="B94" s="39"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="40" t="n">
         <f aca="false">F15+F28+(F40-125000)+F47+F52+F58+(F71-4460.4-19915.99)+F77+F82+F87+F91</f>
         <v>414417.07</v>
       </c>
-      <c r="E94" s="40"/>
-      <c r="F94" s="40"/>
-      <c r="G94" s="40"/>
+      <c r="E94" s="41"/>
+      <c r="F94" s="41"/>
+      <c r="G94" s="41"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5019,7 +5023,7 @@
       <c r="G96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="41" t="s">
+      <c r="A97" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6019,8 +6023,8 @@
       <c r="E2" s="44" t="n">
         <v>-14704.95</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7825,12 +7829,12 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="41" t="s">
+      <c r="A91" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="41" t="s">
+      <c r="A92" s="1" t="s">
         <v>259</v>
       </c>
     </row>
@@ -8797,8 +8801,8 @@
       <c r="E2" s="44" t="n">
         <v>-6789.15</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8814,7 +8818,7 @@
       <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -9992,7 +9996,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="33" t="s">
         <v>331</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -10014,7 +10018,7 @@
       <c r="H56" s="67"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="33" t="s">
         <v>331</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -10034,7 +10038,7 @@
       <c r="H57" s="67"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32" t="s">
+      <c r="A58" s="33" t="s">
         <v>331</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -10054,7 +10058,7 @@
       <c r="H58" s="67"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="33" t="s">
         <v>331</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -10788,7 +10792,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="41" t="s">
+      <c r="A92" s="1" t="s">
         <v>385</v>
       </c>
       <c r="E92" s="87" t="n">
@@ -10796,7 +10800,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="41" t="s">
+      <c r="A93" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -11789,8 +11793,8 @@
       <c r="E2" s="44" t="n">
         <v>-21406.71</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11806,7 +11810,7 @@
       <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -11970,7 +11974,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>394</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -11993,7 +11997,7 @@
       <c r="H11" s="67"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>394</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -12016,7 +12020,7 @@
       <c r="H12" s="67"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="33" t="s">
         <v>394</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -12039,7 +12043,7 @@
       <c r="H13" s="67"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="33" t="s">
         <v>399</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -12062,7 +12066,7 @@
       <c r="H14" s="67"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="33" t="s">
         <v>399</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -12210,7 +12214,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="33" t="s">
         <v>74</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -12256,7 +12260,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="33" t="s">
         <v>415</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -12329,7 +12333,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -12350,7 +12354,7 @@
       <c r="H26" s="67"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -12371,7 +12375,7 @@
       <c r="H27" s="67"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -12392,7 +12396,7 @@
       <c r="H28" s="67"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -12415,7 +12419,7 @@
       <c r="H29" s="67"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -12463,7 +12467,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -12511,7 +12515,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="33" t="s">
         <v>422</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -12609,7 +12613,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="33" t="s">
         <v>437</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -12632,7 +12636,7 @@
       <c r="H38" s="67"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="33" t="s">
         <v>437</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -12655,7 +12659,7 @@
       <c r="H39" s="67"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="33" t="s">
         <v>437</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -12703,7 +12707,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="33" t="s">
         <v>437</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -12772,7 +12776,7 @@
       <c r="H44" s="63"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -12795,7 +12799,7 @@
       <c r="H45" s="67"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -12816,7 +12820,7 @@
       <c r="H46" s="67"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -12862,7 +12866,7 @@
       <c r="H48" s="63"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -13692,7 +13696,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="1" t="s">
         <v>509</v>
       </c>
       <c r="C83" s="91"/>
@@ -14782,8 +14786,8 @@
         <f aca="false">'תזרים ספטמבר 2026'!E83</f>
         <v>117658.66</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14799,7 +14803,7 @@
       <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -14963,7 +14967,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>520</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -14988,7 +14992,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>520</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -15013,7 +15017,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="33" t="s">
         <v>521</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -15713,7 +15717,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="29" t="n">
         <v>46307</v>
       </c>
@@ -15736,7 +15740,7 @@
       </c>
       <c r="H42" s="67"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="29" t="n">
         <v>46307</v>
       </c>
@@ -15759,7 +15763,7 @@
       </c>
       <c r="H43" s="67"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="29" t="n">
         <v>46308</v>
       </c>
@@ -15782,7 +15786,7 @@
       </c>
       <c r="H44" s="67"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="29" t="n">
         <v>46308</v>
       </c>
@@ -15803,9 +15807,11 @@
       <c r="G45" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H45" s="67"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="67" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="29" t="n">
         <v>46308</v>
       </c>
@@ -15828,7 +15834,7 @@
       </c>
       <c r="H46" s="67"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15851,7 +15857,7 @@
       </c>
       <c r="H47" s="67"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15874,7 +15880,7 @@
       </c>
       <c r="H48" s="67"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15895,7 +15901,7 @@
       </c>
       <c r="H49" s="67"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15918,7 +15924,7 @@
       </c>
       <c r="H50" s="67"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15943,7 +15949,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15968,7 +15974,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="29" t="n">
         <v>46309</v>
       </c>
@@ -15993,7 +15999,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16018,7 +16024,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16043,7 +16049,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16068,7 +16074,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16093,7 +16099,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16118,7 +16124,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="29" t="n">
         <v>46309</v>
       </c>
@@ -16141,7 +16147,7 @@
       </c>
       <c r="H59" s="67"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="29" t="n">
         <v>46310</v>
       </c>
@@ -16166,7 +16172,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="29" t="n">
         <v>46310</v>
       </c>
@@ -16192,7 +16198,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="1" t="s">
         <v>582</v>
       </c>
       <c r="C62" s="91"/>
@@ -16235,7 +16241,7 @@
       <c r="C66" s="96"/>
       <c r="D66" s="90" t="n">
         <f aca="false">SUMIF(H5:H61,"כן",D5:D61)</f>
-        <v>171045.67</v>
+        <v>187565.67</v>
       </c>
       <c r="E66" s="91"/>
     </row>
@@ -16276,17 +16282,17 @@
       <c r="G70" s="94"/>
       <c r="H70" s="94"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C71" s="37" t="s">
+      <c r="C71" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D71" s="37" t="s">
+      <c r="D71" s="38" t="s">
         <v>121</v>
       </c>
       <c r="E71" s="97" t="s">
@@ -16453,7 +16459,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="41" t="s">
+      <c r="A78" s="1" t="s">
         <v>598</v>
       </c>
       <c r="C78" s="91"/>
@@ -17572,16 +17578,16 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="110" t="s">
         <v>613</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="110"/>
       <c r="D11" s="21" t="n">
         <f aca="false">SUM(D6:D10)</f>
         <v>414417.07</v>
       </c>
-      <c r="E11" s="110"/>
+      <c r="E11" s="111"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
@@ -17616,11 +17622,7 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="111"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
+      <c r="A16" s="112"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
@@ -17647,10 +17649,10 @@
       <c r="C18" s="108" t="n">
         <v>208316.3</v>
       </c>
-      <c r="D18" s="112" t="s">
+      <c r="D18" s="113" t="s">
         <v>618</v>
       </c>
-      <c r="E18" s="113"/>
+      <c r="E18" s="114"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="107" t="s">
@@ -17662,10 +17664,10 @@
       <c r="C19" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="112" t="s">
+      <c r="D19" s="113" t="s">
         <v>621</v>
       </c>
-      <c r="E19" s="113"/>
+      <c r="E19" s="114"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="107" t="s">
@@ -17677,10 +17679,10 @@
       <c r="C20" s="108" t="n">
         <v>18262.9</v>
       </c>
-      <c r="D20" s="112" t="s">
+      <c r="D20" s="113" t="s">
         <v>623</v>
       </c>
-      <c r="E20" s="113"/>
+      <c r="E20" s="114"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="107" t="s">
@@ -17692,10 +17694,10 @@
       <c r="C21" s="108" t="n">
         <v>44571</v>
       </c>
-      <c r="D21" s="112" t="s">
+      <c r="D21" s="113" t="s">
         <v>623</v>
       </c>
-      <c r="E21" s="113"/>
+      <c r="E21" s="114"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="107" t="s">
@@ -17705,12 +17707,12 @@
         <v>625</v>
       </c>
       <c r="C22" s="108" t="n">
-        <v>16250</v>
-      </c>
-      <c r="D22" s="112" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="113" t="s">
         <v>626</v>
       </c>
-      <c r="E22" s="113"/>
+      <c r="E22" s="114"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="107" t="s">
@@ -17722,10 +17724,10 @@
       <c r="C23" s="108" t="n">
         <v>107834.3</v>
       </c>
-      <c r="D23" s="112" t="s">
+      <c r="D23" s="113" t="s">
         <v>628</v>
       </c>
-      <c r="E23" s="113"/>
+      <c r="E23" s="114"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="107" t="s">
@@ -17737,10 +17739,10 @@
       <c r="C24" s="108" t="n">
         <v>35432.57</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="D24" s="113" t="s">
         <v>630</v>
       </c>
-      <c r="E24" s="113"/>
+      <c r="E24" s="114"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="107" t="s">
@@ -17752,35 +17754,35 @@
       <c r="C25" s="108" t="n">
         <v>12676.86</v>
       </c>
-      <c r="D25" s="112" t="s">
+      <c r="D25" s="113" t="s">
         <v>633</v>
       </c>
-      <c r="E25" s="113"/>
+      <c r="E25" s="114"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="110" t="s">
         <v>634</v>
       </c>
-      <c r="B26" s="19"/>
+      <c r="B26" s="110"/>
       <c r="C26" s="21" t="n">
         <f aca="false">SUM(C18:C25)</f>
-        <v>443343.93</v>
-      </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
+        <v>427093.93</v>
+      </c>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="39" t="s">
         <v>635</v>
       </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39" t="n">
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40" t="n">
         <f aca="false">D11+C19+C22+C25</f>
-        <v>443343.93</v>
-      </c>
-      <c r="E28" s="40"/>
+        <v>427093.93</v>
+      </c>
+      <c r="E28" s="41"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17800,239 +17802,239 @@
       <c r="D32" s="89"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="114" t="s">
+      <c r="A33" s="115" t="s">
         <v>637</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="115" t="s">
         <v>638</v>
       </c>
-      <c r="C33" s="114" t="s">
+      <c r="C33" s="115" t="s">
         <v>603</v>
       </c>
-      <c r="D33" s="115" t="s">
+      <c r="D33" s="116" t="s">
         <v>639</v>
       </c>
-      <c r="E33" s="116"/>
+      <c r="E33" s="117"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="117" t="s">
+      <c r="A34" s="118" t="s">
         <v>640</v>
       </c>
-      <c r="B34" s="117" t="s">
+      <c r="B34" s="118" t="s">
         <v>641</v>
       </c>
-      <c r="C34" s="118" t="n">
+      <c r="C34" s="119" t="n">
         <v>15803.8</v>
       </c>
-      <c r="D34" s="119" t="s">
+      <c r="D34" s="120" t="s">
         <v>642</v>
       </c>
-      <c r="E34" s="116"/>
+      <c r="E34" s="117"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="118" t="s">
         <v>643</v>
       </c>
-      <c r="B35" s="117" t="s">
+      <c r="B35" s="118" t="s">
         <v>644</v>
       </c>
-      <c r="C35" s="118" t="n">
+      <c r="C35" s="119" t="n">
         <v>2367</v>
       </c>
-      <c r="D35" s="119" t="s">
+      <c r="D35" s="120" t="s">
         <v>645</v>
       </c>
-      <c r="E35" s="116"/>
+      <c r="E35" s="117"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="118" t="s">
         <v>646</v>
       </c>
-      <c r="B36" s="117" t="s">
+      <c r="B36" s="118" t="s">
         <v>647</v>
       </c>
-      <c r="C36" s="118" t="n">
+      <c r="C36" s="119" t="n">
         <v>8425</v>
       </c>
-      <c r="D36" s="119" t="s">
+      <c r="D36" s="120" t="s">
         <v>648</v>
       </c>
-      <c r="E36" s="116"/>
+      <c r="E36" s="117"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="117" t="s">
+      <c r="A37" s="118" t="s">
         <v>643</v>
       </c>
-      <c r="B37" s="117" t="s">
+      <c r="B37" s="118" t="s">
         <v>649</v>
       </c>
-      <c r="C37" s="118" t="n">
+      <c r="C37" s="119" t="n">
         <v>91496</v>
       </c>
-      <c r="D37" s="119"/>
-      <c r="E37" s="116"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="117"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="117" t="s">
+      <c r="A38" s="118" t="s">
         <v>650</v>
       </c>
-      <c r="B38" s="117" t="s">
+      <c r="B38" s="118" t="s">
         <v>651</v>
       </c>
-      <c r="C38" s="118" t="n">
+      <c r="C38" s="119" t="n">
         <v>112041</v>
       </c>
-      <c r="D38" s="119" t="s">
+      <c r="D38" s="120" t="s">
         <v>652</v>
       </c>
-      <c r="E38" s="116"/>
+      <c r="E38" s="117"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="117" t="s">
+      <c r="A39" s="118" t="s">
         <v>653</v>
       </c>
-      <c r="B39" s="117" t="s">
+      <c r="B39" s="118" t="s">
         <v>654</v>
       </c>
-      <c r="C39" s="118" t="n">
+      <c r="C39" s="119" t="n">
         <v>120397</v>
       </c>
-      <c r="D39" s="119" t="s">
+      <c r="D39" s="120" t="s">
         <v>655</v>
       </c>
-      <c r="E39" s="116"/>
+      <c r="E39" s="117"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="117" t="s">
+      <c r="A40" s="118" t="s">
         <v>656</v>
       </c>
-      <c r="B40" s="117" t="s">
+      <c r="B40" s="118" t="s">
         <v>657</v>
       </c>
-      <c r="C40" s="118" t="n">
+      <c r="C40" s="119" t="n">
         <v>163</v>
       </c>
-      <c r="D40" s="119" t="s">
+      <c r="D40" s="120" t="s">
         <v>658</v>
       </c>
-      <c r="E40" s="116"/>
+      <c r="E40" s="117"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="117" t="s">
+      <c r="A41" s="118" t="s">
         <v>643</v>
       </c>
-      <c r="B41" s="117" t="s">
+      <c r="B41" s="118" t="s">
         <v>659</v>
       </c>
-      <c r="C41" s="118" t="n">
+      <c r="C41" s="119" t="n">
         <v>55833</v>
       </c>
-      <c r="D41" s="119" t="s">
+      <c r="D41" s="120" t="s">
         <v>652</v>
       </c>
-      <c r="E41" s="116"/>
+      <c r="E41" s="117"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="117" t="s">
+      <c r="A42" s="118" t="s">
         <v>660</v>
       </c>
-      <c r="B42" s="117" t="s">
+      <c r="B42" s="118" t="s">
         <v>661</v>
       </c>
-      <c r="C42" s="118" t="n">
+      <c r="C42" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="119" t="s">
+      <c r="D42" s="120" t="s">
         <v>662</v>
       </c>
-      <c r="E42" s="116"/>
+      <c r="E42" s="117"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="117" t="s">
+      <c r="A43" s="118" t="s">
         <v>646</v>
       </c>
-      <c r="B43" s="117" t="s">
+      <c r="B43" s="118" t="s">
         <v>663</v>
       </c>
-      <c r="C43" s="118" t="n">
+      <c r="C43" s="119" t="n">
         <v>66573</v>
       </c>
-      <c r="D43" s="119" t="s">
+      <c r="D43" s="120" t="s">
         <v>652</v>
       </c>
-      <c r="E43" s="116"/>
+      <c r="E43" s="117"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="117" t="s">
+      <c r="A44" s="118" t="s">
         <v>664</v>
       </c>
-      <c r="B44" s="117" t="s">
+      <c r="B44" s="118" t="s">
         <v>665</v>
       </c>
-      <c r="C44" s="118" t="n">
+      <c r="C44" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="119" t="s">
+      <c r="D44" s="120" t="s">
         <v>666</v>
       </c>
-      <c r="E44" s="116"/>
+      <c r="E44" s="117"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="117" t="s">
+      <c r="A45" s="118" t="s">
         <v>667</v>
       </c>
-      <c r="B45" s="117" t="s">
+      <c r="B45" s="118" t="s">
         <v>668</v>
       </c>
-      <c r="C45" s="118" t="n">
+      <c r="C45" s="119" t="n">
         <v>7723</v>
       </c>
-      <c r="D45" s="119" t="s">
+      <c r="D45" s="120" t="s">
         <v>669</v>
       </c>
-      <c r="E45" s="116"/>
+      <c r="E45" s="117"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="117" t="s">
+      <c r="A46" s="118" t="s">
         <v>667</v>
       </c>
-      <c r="B46" s="117" t="s">
+      <c r="B46" s="118" t="s">
         <v>670</v>
       </c>
-      <c r="C46" s="118" t="n">
+      <c r="C46" s="119" t="n">
         <v>19171</v>
       </c>
-      <c r="D46" s="119" t="s">
+      <c r="D46" s="120" t="s">
         <v>671</v>
       </c>
-      <c r="E46" s="116"/>
+      <c r="E46" s="117"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="117" t="s">
+      <c r="A47" s="118" t="s">
         <v>672</v>
       </c>
-      <c r="B47" s="117" t="s">
+      <c r="B47" s="118" t="s">
         <v>673</v>
       </c>
-      <c r="C47" s="118" t="n">
+      <c r="C47" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="119" t="s">
+      <c r="D47" s="120" t="s">
         <v>674</v>
       </c>
-      <c r="E47" s="116"/>
+      <c r="E47" s="117"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="120" t="s">
+      <c r="A48" s="121" t="s">
         <v>675</v>
       </c>
-      <c r="B48" s="121"/>
-      <c r="C48" s="122" t="n">
+      <c r="B48" s="122"/>
+      <c r="C48" s="123" t="n">
         <f aca="false">SUM(C34:C47)</f>
         <v>499992.8</v>
       </c>
-      <c r="D48" s="123"/>
-      <c r="E48" s="116"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="117"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18044,7 +18046,7 @@
       <c r="D50" s="88"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="1" t="s">
         <v>677</v>
       </c>
       <c r="C51" s="91" t="n">
@@ -18052,7 +18054,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="41" t="s">
+      <c r="A52" s="1" t="s">
         <v>678</v>
       </c>
       <c r="C52" s="91" t="n">
@@ -18061,35 +18063,35 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="124" t="s">
+      <c r="A53" s="125" t="s">
         <v>679</v>
       </c>
-      <c r="B53" s="124"/>
-      <c r="C53" s="125" t="n">
+      <c r="B53" s="125"/>
+      <c r="C53" s="126" t="n">
         <f aca="false">C51+C52</f>
         <v>659905.07</v>
       </c>
-      <c r="D53" s="124"/>
+      <c r="D53" s="125"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="1" t="s">
         <v>680</v>
       </c>
       <c r="C54" s="91" t="n">
         <f aca="false">D28</f>
-        <v>443343.93</v>
+        <v>427093.93</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="126" t="s">
+      <c r="A55" s="127" t="s">
         <v>681</v>
       </c>
-      <c r="B55" s="126"/>
-      <c r="C55" s="127" t="n">
+      <c r="B55" s="127"/>
+      <c r="C55" s="128" t="n">
         <f aca="false">C53-C54</f>
-        <v>216561.14</v>
-      </c>
-      <c r="D55" s="126"/>
+        <v>232811.14</v>
+      </c>
+      <c r="D55" s="127"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18101,80 +18103,80 @@
       <c r="D57" s="88"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="128" t="s">
+      <c r="A58" s="129" t="s">
         <v>683</v>
       </c>
-      <c r="B58" s="128" t="s">
+      <c r="B58" s="129" t="s">
         <v>684</v>
       </c>
-      <c r="C58" s="128" t="s">
+      <c r="C58" s="129" t="s">
         <v>685</v>
       </c>
-      <c r="D58" s="128" t="s">
+      <c r="D58" s="129" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="129" t="s">
+      <c r="A59" s="130" t="s">
         <v>687</v>
       </c>
-      <c r="B59" s="128" t="s">
+      <c r="B59" s="129" t="s">
         <v>688</v>
       </c>
-      <c r="C59" s="130" t="n">
+      <c r="C59" s="131" t="n">
         <v>2273</v>
       </c>
-      <c r="D59" s="130" t="n">
+      <c r="D59" s="131" t="n">
         <v>2140</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="128" t="s">
+      <c r="A60" s="129" t="s">
         <v>689</v>
       </c>
-      <c r="B60" s="128" t="s">
+      <c r="B60" s="129" t="s">
         <v>690</v>
       </c>
-      <c r="C60" s="130" t="n">
+      <c r="C60" s="131" t="n">
         <v>1184</v>
       </c>
-      <c r="D60" s="130" t="n">
+      <c r="D60" s="131" t="n">
         <v>1202</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="128" t="s">
+      <c r="A61" s="129" t="s">
         <v>691</v>
       </c>
-      <c r="B61" s="128" t="s">
+      <c r="B61" s="129" t="s">
         <v>690</v>
       </c>
-      <c r="C61" s="130" t="n">
+      <c r="C61" s="131" t="n">
         <v>2248</v>
       </c>
-      <c r="D61" s="130" t="n">
+      <c r="D61" s="131" t="n">
         <v>3552</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="124" t="s">
+      <c r="A62" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="B62" s="124"/>
-      <c r="C62" s="125" t="n">
+      <c r="B62" s="125"/>
+      <c r="C62" s="126" t="n">
         <v>5705</v>
       </c>
-      <c r="D62" s="125" t="n">
+      <c r="D62" s="126" t="n">
         <v>6894</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="124" t="s">
+      <c r="A63" s="125" t="s">
         <v>692</v>
       </c>
-      <c r="B63" s="124"/>
-      <c r="C63" s="125"/>
-      <c r="D63" s="125" t="n">
+      <c r="B63" s="125"/>
+      <c r="C63" s="126"/>
+      <c r="D63" s="126" t="n">
         <v>12599</v>
       </c>
     </row>

--- a/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים ישר סופי.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="697">
   <si>
     <t xml:space="preserve">חוב לתאגידי כוח אדם  |  ישר שירותי קרקע לקבלן ולפועל בע"מ  |  ינואר–ספטמבר 2026</t>
   </si>
@@ -357,7 +357,7 @@
     <t xml:space="preserve">✅ שולם 09/09/2026 בהעברה דיגיטלית - 75,065 ₪ (סכום מאומת מול הבנק, לא אומדן). עדיין יש לקבל את מסמך החשבונית עצמו מהתאגיד</t>
   </si>
   <si>
-    <t xml:space="preserve">ג.ד. קלמרה הנדסה ובנייה בע"מ   |   ח.פ. 516489689</t>
+    <t xml:space="preserve">ג.ד. קלמרה הנדסה ובנייה בע"מ   |   ח.פ. 516489689   |   ספטמבר: משלם גם את עובדי ד.י שרף (בעיית חשבונית מול שרף) - ממתין לחשבונית מס</t>
   </si>
   <si>
     <t xml:space="preserve">14/09/2026</t>
@@ -366,13 +366,25 @@
     <t xml:space="preserve">22/09 ✅ שולם</t>
   </si>
   <si>
+    <t xml:space="preserve">ספטמבר (עובדי ד.י שרף + עמלה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חשבון עסקה 1032 · ממתין לחשבונית מס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ שולם 14/10/2026 - 30,647 ₪ (מאומת מול הבנק). התשלום עבור עובדי ד.י שרף + עמלת קלמרה, דרך קלמרה כי הייתה בעיה לקבל חשבונית מד.י שרף. ⏳ קלמרה יוציא חשבונית מס על הכל</t>
+  </si>
+  <si>
     <t xml:space="preserve">💰  סך חוב פתוח לכל התאגידים   (✱ לא כולל BMG פברואר+אפריל | לא כולל פאנג יוני 125,000 - צ׳ק 5000346 ב-25/10)</t>
   </si>
   <si>
     <t xml:space="preserve">✱ יתרת פאנג יוני: צ׳ק 24/09/2026 ירד ✅ · נותר צ׳ק 25/10/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ כל חשבוניות אוגוסט התקבלו. שולמו: פסגת ליאם, שרף (09/09), פניני התכלת, ד.יוחאי, אחים לימור, ג.ד קלמרה, פוגין (22/09), שי-לי (24/09), BMG (05/10). נותרה לתשלום: פאנג. ✅ פסגת ליאם ספטמבר (50156) שולם 06/10 - 12,685.71 ₪. שרף - עדיין ממתין למסמך החשבונית עצמו. ⏳ פוגין ספטמבר (01/000938) - 18,262.90 ₪ לתשלום 25/10. ⏳ שי-לי ספטמבר (230747) - 44,571 ₪ לתשלום 25/10. ⏳ אחים לימור ספטמבר (חשבון עסקה 8052) - 107,834.30 ₪.</t>
+    <t xml:space="preserve">✅ כל חשבוניות אוגוסט התקבלו. שולמו: פסגת ליאם, שרף (09/09), פניני התכלת, ד.יוחאי, אחים לימור, ג.ד קלמרה, פוגין (22/09), שי-לי (24/09), BMG (05/10). נותרה לתשלום: פאנג. ✅ פסגת ליאם ספטמבר (50156) שולם 06/10 - 12,685.71 ₪. שרף - עדיין ממתין למסמך החשבונית עצמו (אוגוסט). ✅ שרף ספטמבר שולם 14/10 דרך ג.ד קלמרה (30,647 כולל עמלת קלמרה) - ⏳ ממתין לחשבונית מס מקלמרה על הכל. ⏳ פוגין ספטמבר (01/000938) - 18,262.90 ₪ לתשלום 25/10. ⏳ שי-לי ספטמבר (230747) - 44,571 ₪ לתשלום 25/10. ⏳ אחים לימור ספטמבר (חשבון עסקה 8052) - 107,834.30 ₪.</t>
   </si>
   <si>
     <t xml:space="preserve">מועדי תשלום קבועים לתאגידים: עוצמת התמרון - ה-15 לחודש · פניני התכלת - ה-20 לחודש · יוחאי - ה-20 לחודש · שי-לי - ה-25 לחודש · פוגין - ה-25 לחודש</t>
@@ -1737,10 +1749,10 @@
     <t xml:space="preserve">חוזר לחשבון (קוזז מול הפדיון - נטו 0, הצפי של 45,605.61 כהכנסה לא התממש)</t>
   </si>
   <si>
-    <t xml:space="preserve">ג.ד קלמרה - תשלום חשבון עסקה 1032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ לאמת עבור מה ולאיזה חודש (הסכם מסגרת ד.יוחאי + ג.ד קלמרה)</t>
+    <t xml:space="preserve">ג.ד קלמרה - תשלום עבור עובדי ד.י שרף + עמלת קלמרה (חשבון עסקה 1032)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תשלום התאגיד ד.י שרף + העמלה של קלמרה, דרך קלמרה - כי הייתה בעיה לקבל חשבונית מד.י שרף. ⏳ קלמרה יוציא חשבונית מס על כל הסכום (לפי שמואל 15/10)</t>
   </si>
   <si>
     <t xml:space="preserve">✅ תשלום 1 מתוך 8 (אוקטובר 2026) ירד 14/10 · נותרו 7 תשלומים (נובמבר 2026 עד מאי 2027) - ב-10 לחודש</t>
@@ -1776,7 +1788,7 @@
     <t xml:space="preserve">יתרה – 15/10/2026 (מאומת מול הבנק: 159,912.27 ₪)</t>
   </si>
   <si>
-    <t xml:space="preserve">הערה: הנתונים עד 15/10/2026 מאומתים מול דוח בנק לאומי (159,912.27 ₪, דוח 15/10/2026; תנועות 15/10 אינן סופיות). ב-12-13/10 נכנסו ברגשטיין 156,403 (40119 נסגר), גרייטדור 26,513 (על חשבון 40113) ואביאלי 15,741; יצא שיק 5000289 16,520 לש. מינסקי יזמות. ב-14/10 יצאו ISRAEL CARGO 19,770 (תשלום 1/8), ג.ד קלמרה 30,647, שכירויות דירות 28,300, סגירות התחשבנות קבאסה 3,678 וקוט 2,418 ופרידמן 400. פיקדון 45,605 נפדה וקוזז - נטו 0. ב-15/10 חיובי כרטיסים 5,883.18.</t>
+    <t xml:space="preserve">הערה: הנתונים עד 15/10/2026 מאומתים מול דוח בנק לאומי (159,912.27 ₪, דוח 15/10/2026; תנועות 15/10 אינן סופיות). ב-12-13/10 נכנסו ברגשטיין 156,403 (40119 נסגר), גרייטדור 26,513 (על חשבון 40113) ואביאלי 15,741; יצא שיק 5000289 16,520 לש. מינסקי יזמות. ב-14/10 יצאו ISRAEL CARGO 19,770 (תשלום 1/8), ג.ד קלמרה 30,647 (עבור עובדי ד.י שרף + עמלת קלמרה), שכירויות דירות 28,300, סגירות התחשבנות קבאסה 3,678 וקוט 2,418 ופרידמן 400. פיקדון 45,605 נפדה וקוזז - נטו 0. ב-15/10 חיובי כרטיסים 5,883.18.</t>
   </si>
   <si>
     <t xml:space="preserve">סה"כ הוצאות שכן שייכות לחודש (שכירות, קבועות, כרטיסי אשראי, מסים)</t>
@@ -4970,40 +4982,58 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="19" t="s">
+      <c r="A91" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>30647</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>30647</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <f aca="false">D91-E91</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="21" t="n">
-        <v>4085</v>
-      </c>
-      <c r="E91" s="21" t="n">
-        <v>4085</v>
-      </c>
-      <c r="F91" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="20"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
+      <c r="D92" s="21" t="n">
+        <f aca="false">SUM(D90:D91)</f>
+        <v>34732</v>
+      </c>
+      <c r="E92" s="21" t="n">
+        <f aca="false">SUM(E90:E91)</f>
+        <v>34732</v>
+      </c>
+      <c r="F92" s="21" t="n">
+        <f aca="false">SUM(F90:F91)</f>
+        <v>0</v>
+      </c>
       <c r="G92" s="20"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="39" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B94" s="39"/>
       <c r="C94" s="39"/>
       <c r="D94" s="40" t="n">
-        <f aca="false">F15+F28+(F40-125000)+F47+F52+F58+(F71-4460.4-19915.99)+F77+F82+F87+F91</f>
+        <f aca="false">F15+F28+(F40-125000)+F47+F52+F58+(F71-4460.4-19915.99)+F77+F82+F87+F92</f>
         <v>414417.07</v>
       </c>
       <c r="E94" s="41"/>
@@ -5013,7 +5043,7 @@
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5024,13 +5054,13 @@
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6004,7 +6034,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6015,7 +6045,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -6032,30 +6062,30 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="45" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="48" t="n">
@@ -6065,18 +6095,18 @@
         <v>-14794.95</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C6" s="53"/>
       <c r="D6" s="54" t="n">
@@ -6086,18 +6116,18 @@
         <v>-23959.95</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="45" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="48" t="n">
@@ -6107,18 +6137,18 @@
         <v>-24047.4</v>
       </c>
       <c r="F7" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C8" s="47"/>
       <c r="D8" s="48" t="n">
@@ -6128,18 +6158,18 @@
         <v>-25980.6</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C9" s="47"/>
       <c r="D9" s="48" t="n">
@@ -6149,18 +6179,18 @@
         <v>-32066.34</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="48" t="n">
@@ -6170,18 +6200,18 @@
         <v>-34064.23</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C11" s="47"/>
       <c r="D11" s="48" t="n">
@@ -6191,18 +6221,18 @@
         <v>-34514.23</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>30000</v>
@@ -6212,18 +6242,18 @@
         <v>-4514.23</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C13" s="53"/>
       <c r="D13" s="54" t="n">
@@ -6233,18 +6263,18 @@
         <v>-7014.23</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="48" t="n">
@@ -6254,18 +6284,18 @@
         <v>-7339.05</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="45" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="48" t="n">
@@ -6275,18 +6305,18 @@
         <v>-67164.05</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="48" t="n">
@@ -6296,18 +6326,18 @@
         <v>-67209.95</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="48" t="n">
@@ -6317,18 +6347,18 @@
         <v>-67284.85</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G17" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>25000</v>
@@ -6338,18 +6368,18 @@
         <v>-42284.85</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>25000</v>
@@ -6359,18 +6389,18 @@
         <v>-17284.85</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>43158.5</v>
@@ -6380,18 +6410,18 @@
         <v>25873.65</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48" t="n">
@@ -6401,18 +6431,18 @@
         <v>25830.65</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G21" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="48" t="n">
@@ -6422,18 +6452,18 @@
         <v>25826.75</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="51" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C23" s="53"/>
       <c r="D23" s="54" t="n">
@@ -6443,18 +6473,18 @@
         <v>7536.75000000001</v>
       </c>
       <c r="F23" s="56" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="54" t="n">
@@ -6464,18 +6494,18 @@
         <v>7187.73000000001</v>
       </c>
       <c r="F24" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B25" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C25" s="53"/>
       <c r="D25" s="54" t="n">
@@ -6485,18 +6515,18 @@
         <v>6676.74000000001</v>
       </c>
       <c r="F25" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B26" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C26" s="53"/>
       <c r="D26" s="54" t="n">
@@ -6506,18 +6536,18 @@
         <v>5836.15000000001</v>
       </c>
       <c r="F26" s="56" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G26" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C27" s="53"/>
       <c r="D27" s="54" t="n">
@@ -6527,18 +6557,18 @@
         <v>4725.19000000001</v>
       </c>
       <c r="F27" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="54" t="n">
@@ -6548,18 +6578,18 @@
         <v>3426.03000000001</v>
       </c>
       <c r="F28" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G28" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C29" s="53"/>
       <c r="D29" s="54" t="n">
@@ -6569,18 +6599,18 @@
         <v>627.730000000007</v>
       </c>
       <c r="F29" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="45" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C30" s="47"/>
       <c r="D30" s="48" t="n">
@@ -6590,10 +6620,10 @@
         <v>-8192.26999999999</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6601,7 +6631,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C31" s="47"/>
       <c r="D31" s="48" t="n">
@@ -6611,10 +6641,10 @@
         <v>-8692.26999999999</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6622,7 +6652,7 @@
         <v>68</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>26697.5</v>
@@ -6632,10 +6662,10 @@
         <v>18005.23</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6643,7 +6673,7 @@
         <v>68</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112180.24</v>
@@ -6653,10 +6683,10 @@
         <v>130185.47</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6664,7 +6694,7 @@
         <v>68</v>
       </c>
       <c r="B34" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C34" s="53"/>
       <c r="D34" s="54" t="n">
@@ -6674,10 +6704,10 @@
         <v>124138.47</v>
       </c>
       <c r="F34" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G34" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6685,7 +6715,7 @@
         <v>68</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>25772</v>
@@ -6695,10 +6725,10 @@
         <v>149910.47</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6706,7 +6736,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>42075.85</v>
@@ -6716,10 +6746,10 @@
         <v>191986.32</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6727,7 +6757,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>182847</v>
@@ -6737,18 +6767,18 @@
         <v>374833.32</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C38" s="53"/>
       <c r="D38" s="54" t="n">
@@ -6758,18 +6788,18 @@
         <v>363953.32</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G38" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B39" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C39" s="53"/>
       <c r="D39" s="54" t="n">
@@ -6779,18 +6809,18 @@
         <v>349953.32</v>
       </c>
       <c r="F39" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B40" s="46" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C40" s="47"/>
       <c r="D40" s="48" t="n">
@@ -6800,18 +6830,18 @@
         <v>333433.32</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G40" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B41" s="46" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C41" s="47"/>
       <c r="D41" s="48" t="n">
@@ -6821,18 +6851,18 @@
         <v>233433.32</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C42" s="53"/>
       <c r="D42" s="54" t="n">
@@ -6842,18 +6872,18 @@
         <v>220453.32</v>
       </c>
       <c r="F42" s="56" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C43" s="53"/>
       <c r="D43" s="54" t="n">
@@ -6863,18 +6893,18 @@
         <v>211603.32</v>
       </c>
       <c r="F43" s="56" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C44" s="47"/>
       <c r="D44" s="48" t="n">
@@ -6884,18 +6914,18 @@
         <v>201944.32</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C45" s="47"/>
       <c r="D45" s="48" t="n">
@@ -6905,18 +6935,18 @@
         <v>201439.87</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G45" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>2.89</v>
@@ -6926,18 +6956,18 @@
         <v>201442.76</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>45593.63</v>
@@ -6947,18 +6977,18 @@
         <v>247036.39</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C48" s="47"/>
       <c r="D48" s="48" t="n">
@@ -6968,18 +6998,18 @@
         <v>201439.87</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G48" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C49" s="47"/>
       <c r="D49" s="48" t="n">
@@ -6989,18 +7019,18 @@
         <v>201089.74</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G49" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>6000</v>
@@ -7010,18 +7040,18 @@
         <v>207089.74</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B51" s="52" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C51" s="53"/>
       <c r="D51" s="54" t="n">
@@ -7031,18 +7061,18 @@
         <v>200089.74</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C52" s="53"/>
       <c r="D52" s="54" t="n">
@@ -7052,18 +7082,18 @@
         <v>190489.74</v>
       </c>
       <c r="F52" s="56" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G52" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="54" t="n">
@@ -7073,18 +7103,18 @@
         <v>186489.74</v>
       </c>
       <c r="F53" s="56" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C54" s="53"/>
       <c r="D54" s="54" t="n">
@@ -7094,18 +7124,18 @@
         <v>182489.74</v>
       </c>
       <c r="F54" s="56" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G54" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B55" s="52" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C55" s="53"/>
       <c r="D55" s="54" t="n">
@@ -7115,18 +7145,18 @@
         <v>179489.74</v>
       </c>
       <c r="F55" s="56" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="48" t="n">
@@ -7136,18 +7166,18 @@
         <v>177719.74</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G56" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="51" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B57" s="52" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C57" s="53"/>
       <c r="D57" s="54" t="n">
@@ -7157,18 +7187,18 @@
         <v>173019.74</v>
       </c>
       <c r="F57" s="56" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="45" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C58" s="47"/>
       <c r="D58" s="48" t="n">
@@ -7178,18 +7208,18 @@
         <v>165052.11</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G58" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="45" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C59" s="47"/>
       <c r="D59" s="48" t="n">
@@ -7199,18 +7229,18 @@
         <v>154924.44</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G59" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>35643.38</v>
@@ -7220,18 +7250,18 @@
         <v>190567.82</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="45" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C61" s="47"/>
       <c r="D61" s="48" t="n">
@@ -7241,18 +7271,18 @@
         <v>186772.05</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G61" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>2360</v>
@@ -7262,18 +7292,18 @@
         <v>189132.05</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>20000</v>
@@ -7283,18 +7313,18 @@
         <v>209132.05</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C64" s="9" t="n">
         <v>7174.4</v>
@@ -7304,18 +7334,18 @@
         <v>216306.45</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C65" s="9" t="n">
         <v>29658</v>
@@ -7325,18 +7355,18 @@
         <v>245964.45</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C66" s="9" t="n">
         <v>63148</v>
@@ -7346,18 +7376,18 @@
         <v>309112.45</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="45" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C67" s="47"/>
       <c r="D67" s="48" t="n">
@@ -7367,18 +7397,18 @@
         <v>309037.55</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G67" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="51" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B68" s="52" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C68" s="53"/>
       <c r="D68" s="54" t="n">
@@ -7388,18 +7418,18 @@
         <v>307680.55</v>
       </c>
       <c r="F68" s="56" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="45" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C69" s="47"/>
       <c r="D69" s="48" t="n">
@@ -7409,18 +7439,18 @@
         <v>241300.11</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G69" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>40000</v>
@@ -7430,18 +7460,18 @@
         <v>281300.11</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="45" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C71" s="47"/>
       <c r="D71" s="48" t="n">
@@ -7451,18 +7481,18 @@
         <v>277202.33</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G71" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="51" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C72" s="53"/>
       <c r="D72" s="54" t="n">
@@ -7472,18 +7502,18 @@
         <v>275377.33</v>
       </c>
       <c r="F72" s="56" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G72" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="45" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B73" s="46" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C73" s="47"/>
       <c r="D73" s="48" t="n">
@@ -7493,18 +7523,18 @@
         <v>249603.73</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G73" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="45" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C74" s="47"/>
       <c r="D74" s="48" t="n">
@@ -7514,18 +7544,18 @@
         <v>245300.73</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G74" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="45" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C75" s="47"/>
       <c r="D75" s="48" t="n">
@@ -7535,18 +7565,18 @@
         <v>80374.49</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G75" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C76" s="9" t="n">
         <v>150119.5</v>
@@ -7556,18 +7586,18 @@
         <v>230493.99</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="45" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C77" s="47"/>
       <c r="D77" s="48" t="n">
@@ -7577,18 +7607,18 @@
         <v>98031.99</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G77" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="45" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B78" s="46" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C78" s="47"/>
       <c r="D78" s="48" t="n">
@@ -7598,18 +7628,18 @@
         <v>-1968.00999999998</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G78" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C79" s="9" t="n">
         <v>32951</v>
@@ -7619,18 +7649,18 @@
         <v>30982.99</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C80" s="9" t="n">
         <v>5.5</v>
@@ -7640,18 +7670,18 @@
         <v>30988.49</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="51" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C81" s="53"/>
       <c r="D81" s="54" t="n">
@@ -7661,18 +7691,18 @@
         <v>25868.49</v>
       </c>
       <c r="F81" s="56" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G81" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C82" s="9" t="n">
         <v>40000</v>
@@ -7682,18 +7712,18 @@
         <v>65868.49</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="45" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B83" s="46" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C83" s="47"/>
       <c r="D83" s="48" t="n">
@@ -7703,10 +7733,10 @@
         <v>-4968.50999999998</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G83" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7714,7 +7744,7 @@
         <v>94</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C84" s="9" t="n">
         <v>25000</v>
@@ -7724,10 +7754,10 @@
         <v>20031.49</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7735,7 +7765,7 @@
         <v>36</v>
       </c>
       <c r="B85" s="52" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C85" s="53"/>
       <c r="D85" s="54" t="n">
@@ -7745,10 +7775,10 @@
         <v>14975.49</v>
       </c>
       <c r="F85" s="56" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G85" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7756,7 +7786,7 @@
         <v>36</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C86" s="53"/>
       <c r="D86" s="54" t="n">
@@ -7766,10 +7796,10 @@
         <v>10975.49</v>
       </c>
       <c r="F86" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G86" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7777,7 +7807,7 @@
         <v>36</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C87" s="9" t="n">
         <v>25000</v>
@@ -7787,10 +7817,10 @@
         <v>35975.49</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7798,7 +7828,7 @@
         <v>36</v>
       </c>
       <c r="B88" s="46" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C88" s="47"/>
       <c r="D88" s="48" t="n">
@@ -7808,15 +7838,15 @@
         <v>-6789.15</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G88" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="59" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B89" s="52"/>
       <c r="C89" s="53"/>
@@ -7830,12 +7860,12 @@
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8782,7 +8812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8793,7 +8823,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -8810,33 +8840,33 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H4" s="61" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="45" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="48" t="n">
@@ -8846,19 +8876,19 @@
         <v>-7389.15</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="53"/>
       <c r="D6" s="54" t="n">
@@ -8868,21 +8898,21 @@
         <v>-7491.45</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="54" t="n">
@@ -8892,21 +8922,21 @@
         <v>-15458.67</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="54" t="n">
@@ -8916,21 +8946,21 @@
         <v>-17984.77</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H8" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="54" t="n">
@@ -8940,21 +8970,21 @@
         <v>-22471.3</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H9" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C10" s="53"/>
       <c r="D10" s="54" t="n">
@@ -8964,21 +8994,21 @@
         <v>-31638.3</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H10" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2284.05</v>
@@ -8988,19 +9018,19 @@
         <v>-29354.25</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H11" s="67"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>64257.58</v>
@@ -9010,19 +9040,19 @@
         <v>34903.33</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H12" s="67"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C13" s="53"/>
       <c r="D13" s="54" t="n">
@@ -9032,21 +9062,21 @@
         <v>30995.33</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H13" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>10089</v>
@@ -9056,19 +9086,19 @@
         <v>41084.33</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H14" s="67"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>17098</v>
@@ -9078,19 +9108,19 @@
         <v>58182.33</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H15" s="67"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>40614.42</v>
@@ -9101,16 +9131,16 @@
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H16" s="67"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C17" s="53"/>
       <c r="D17" s="54" t="n">
@@ -9120,21 +9150,21 @@
         <v>98614.25</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H17" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>50588</v>
@@ -9145,16 +9175,16 @@
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H18" s="67"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="51" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C19" s="53"/>
       <c r="D19" s="54" t="n">
@@ -9164,21 +9194,21 @@
         <v>130912.25</v>
       </c>
       <c r="F19" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H19" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="48" t="n">
@@ -9188,21 +9218,21 @@
         <v>113814.05</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="51" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C21" s="53"/>
       <c r="D21" s="54" t="n">
@@ -9212,21 +9242,21 @@
         <v>111314.05</v>
       </c>
       <c r="F21" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="51" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="54" t="n">
@@ -9236,21 +9266,21 @@
         <v>110901.59</v>
       </c>
       <c r="F22" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>282192.28</v>
@@ -9260,10 +9290,10 @@
         <v>393093.87</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H23" s="67"/>
     </row>
@@ -9272,7 +9302,7 @@
         <v>71</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>50000</v>
@@ -9283,7 +9313,7 @@
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H24" s="67"/>
     </row>
@@ -9292,7 +9322,7 @@
         <v>71</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>8177.4</v>
@@ -9302,10 +9332,10 @@
         <v>451271.27</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H25" s="67"/>
     </row>
@@ -9314,7 +9344,7 @@
         <v>71</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>25772</v>
@@ -9324,10 +9354,10 @@
         <v>477043.27</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H26" s="67"/>
     </row>
@@ -9336,7 +9366,7 @@
         <v>71</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>102940.84</v>
@@ -9346,10 +9376,10 @@
         <v>579984.11</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H27" s="67"/>
     </row>
@@ -9358,7 +9388,7 @@
         <v>71</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>174158.56</v>
@@ -9368,19 +9398,19 @@
         <v>754142.67</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H28" s="67"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C29" s="53"/>
       <c r="D29" s="54" t="n">
@@ -9390,21 +9420,21 @@
         <v>747233.73</v>
       </c>
       <c r="F29" s="56" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G29" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H29" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>24425.66</v>
@@ -9414,19 +9444,19 @@
         <v>771659.39</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H30" s="67"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="45" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C31" s="47"/>
       <c r="D31" s="48" t="n">
@@ -9436,21 +9466,21 @@
         <v>738708.39</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G31" s="46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H31" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B32" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="54" t="n">
@@ -9460,21 +9490,21 @@
         <v>728485.39</v>
       </c>
       <c r="F32" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G32" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H32" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B33" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C33" s="53"/>
       <c r="D33" s="54" t="n">
@@ -9484,21 +9514,21 @@
         <v>722355.39</v>
       </c>
       <c r="F33" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H33" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="45" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B34" s="46" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C34" s="47"/>
       <c r="D34" s="48" t="n">
@@ -9508,21 +9538,21 @@
         <v>672355.39</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G34" s="46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H34" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="45" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C35" s="47"/>
       <c r="D35" s="48" t="n">
@@ -9532,21 +9562,21 @@
         <v>670795.39</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G35" s="46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H35" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="54" t="n">
@@ -9556,21 +9586,21 @@
         <v>657815.39</v>
       </c>
       <c r="F36" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G36" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C37" s="53"/>
       <c r="D37" s="54" t="n">
@@ -9580,21 +9610,21 @@
         <v>648965.39</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G37" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H37" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C38" s="53" t="n">
         <v>90</v>
@@ -9604,19 +9634,19 @@
         <v>649055.39</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H38" s="65"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B39" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C39" s="53"/>
       <c r="D39" s="54" t="n">
@@ -9626,21 +9656,21 @@
         <v>634055.39</v>
       </c>
       <c r="F39" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C40" s="53"/>
       <c r="D40" s="54" t="n">
@@ -9650,21 +9680,21 @@
         <v>619913.39</v>
       </c>
       <c r="F40" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G40" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B41" s="52" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C41" s="53" t="n">
         <v>32202</v>
@@ -9675,16 +9705,16 @@
       </c>
       <c r="F41" s="56"/>
       <c r="G41" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H41" s="65"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C42" s="53" t="n">
         <v>3188</v>
@@ -9695,16 +9725,16 @@
       </c>
       <c r="F42" s="56"/>
       <c r="G42" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H42" s="65"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C43" s="53"/>
       <c r="D43" s="54" t="n">
@@ -9714,19 +9744,19 @@
         <v>609703.98</v>
       </c>
       <c r="F43" s="56" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G43" s="52" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H43" s="65"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B44" s="52" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C44" s="53" t="n">
         <v>45596.52</v>
@@ -9737,16 +9767,16 @@
       </c>
       <c r="F44" s="56"/>
       <c r="G44" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H44" s="65"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C45" s="53" t="n">
         <v>2.89</v>
@@ -9757,16 +9787,16 @@
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H45" s="65"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B46" s="52" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C46" s="71"/>
       <c r="D46" s="71" t="n">
@@ -9776,21 +9806,21 @@
         <v>650603.39</v>
       </c>
       <c r="F46" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H46" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B47" s="52" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C47" s="71"/>
       <c r="D47" s="71" t="n">
@@ -9800,21 +9830,21 @@
         <v>641003.39</v>
       </c>
       <c r="F47" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H47" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B48" s="52" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C48" s="71"/>
       <c r="D48" s="71" t="n">
@@ -9824,21 +9854,21 @@
         <v>634003.39</v>
       </c>
       <c r="F48" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G48" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H48" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B49" s="52" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C49" s="71"/>
       <c r="D49" s="71" t="n">
@@ -9848,21 +9878,21 @@
         <v>630003.39</v>
       </c>
       <c r="F49" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G49" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H49" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B50" s="52" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C50" s="71"/>
       <c r="D50" s="71" t="n">
@@ -9872,21 +9902,21 @@
         <v>627003.39</v>
       </c>
       <c r="F50" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G50" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B51" s="52" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C51" s="71"/>
       <c r="D51" s="71" t="n">
@@ -9896,21 +9926,21 @@
         <v>623003.39</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G51" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H51" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C52" s="71"/>
       <c r="D52" s="71" t="n">
@@ -9921,18 +9951,18 @@
       </c>
       <c r="F52" s="56"/>
       <c r="G52" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H52" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="59" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C53" s="71"/>
       <c r="D53" s="71" t="n">
@@ -9942,21 +9972,21 @@
         <v>602300.67</v>
       </c>
       <c r="F53" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G53" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H53" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C54" s="71"/>
       <c r="D54" s="71" t="n">
@@ -9967,18 +9997,18 @@
       </c>
       <c r="F54" s="56"/>
       <c r="G54" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H54" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="73" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C55" s="74"/>
       <c r="D55" s="74" t="n">
@@ -9989,18 +10019,18 @@
       </c>
       <c r="F55" s="50"/>
       <c r="G55" s="46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H55" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="33" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C56" s="8" t="n">
         <v>50703.26</v>
@@ -10010,19 +10040,19 @@
         <v>636309.72</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H56" s="67"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="33" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>81389</v>
@@ -10033,16 +10063,16 @@
       </c>
       <c r="F57" s="11"/>
       <c r="G57" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H57" s="67"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="33" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C58" s="8" t="n">
         <v>36064</v>
@@ -10053,16 +10083,16 @@
       </c>
       <c r="F58" s="11"/>
       <c r="G58" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H58" s="67"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="33" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>16425</v>
@@ -10072,19 +10102,19 @@
         <v>770187.72</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H59" s="67"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B60" s="52" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C60" s="71"/>
       <c r="D60" s="71" t="n">
@@ -10094,21 +10124,21 @@
         <v>768830.72</v>
       </c>
       <c r="F60" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H60" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="73" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C61" s="74"/>
       <c r="D61" s="74" t="n">
@@ -10119,18 +10149,18 @@
       </c>
       <c r="F61" s="50"/>
       <c r="G61" s="46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H61" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C62" s="78"/>
       <c r="D62" s="78" t="n">
@@ -10140,21 +10170,21 @@
         <v>758510.1</v>
       </c>
       <c r="F62" s="63" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G62" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H62" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C63" s="78"/>
       <c r="D63" s="78" t="n">
@@ -10165,18 +10195,18 @@
       </c>
       <c r="F63" s="63"/>
       <c r="G63" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H63" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C64" s="78"/>
       <c r="D64" s="78" t="n">
@@ -10187,18 +10217,18 @@
       </c>
       <c r="F64" s="63"/>
       <c r="G64" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H64" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C65" s="78"/>
       <c r="D65" s="78" t="n">
@@ -10208,21 +10238,21 @@
         <v>260019.15</v>
       </c>
       <c r="F65" s="63" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G65" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H65" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C66" s="78"/>
       <c r="D66" s="78" t="n">
@@ -10233,16 +10263,16 @@
       </c>
       <c r="F66" s="63"/>
       <c r="G66" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H66" s="63"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B67" s="67" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C67" s="67" t="n">
         <v>50000</v>
@@ -10252,19 +10282,19 @@
         <v>261135.89</v>
       </c>
       <c r="F67" s="67" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G67" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H67" s="67"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B68" s="67" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C68" s="67" t="n">
         <v>35000</v>
@@ -10275,16 +10305,16 @@
       </c>
       <c r="F68" s="67"/>
       <c r="G68" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H68" s="67"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="63" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B69" s="63" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C69" s="63"/>
       <c r="D69" s="63" t="n">
@@ -10295,18 +10325,18 @@
       </c>
       <c r="F69" s="63"/>
       <c r="G69" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H69" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="63" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B70" s="63" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C70" s="63"/>
       <c r="D70" s="63" t="n">
@@ -10316,21 +10346,21 @@
         <v>223481.17</v>
       </c>
       <c r="F70" s="63" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G70" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H70" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="63" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B71" s="63" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="63" t="n">
@@ -10341,18 +10371,18 @@
       </c>
       <c r="F71" s="63"/>
       <c r="G71" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H71" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="63" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B72" s="63" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="63" t="n">
@@ -10363,18 +10393,18 @@
       </c>
       <c r="F72" s="63"/>
       <c r="G72" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H72" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="63" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B73" s="63" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C73" s="63"/>
       <c r="D73" s="63" t="n">
@@ -10385,18 +10415,18 @@
       </c>
       <c r="F73" s="63"/>
       <c r="G73" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H73" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="63" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B74" s="63" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C74" s="63"/>
       <c r="D74" s="63" t="n">
@@ -10407,18 +10437,18 @@
       </c>
       <c r="F74" s="63"/>
       <c r="G74" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H74" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="67" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B75" s="67" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C75" s="67" t="n">
         <v>9166.24</v>
@@ -10429,16 +10459,16 @@
       </c>
       <c r="F75" s="67"/>
       <c r="G75" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H75" s="67"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="67" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B76" s="67" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C76" s="67" t="n">
         <v>28642</v>
@@ -10448,19 +10478,19 @@
         <v>134651.48</v>
       </c>
       <c r="F76" s="67" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G76" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H76" s="67"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="67" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B77" s="67" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C77" s="67" t="n">
         <v>20000</v>
@@ -10471,16 +10501,16 @@
       </c>
       <c r="F77" s="67"/>
       <c r="G77" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H77" s="67"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="67" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B78" s="67" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C78" s="67" t="n">
         <v>58826</v>
@@ -10490,19 +10520,19 @@
         <v>213477.48</v>
       </c>
       <c r="F78" s="67" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G78" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H78" s="67"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="63" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B79" s="63" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C79" s="63"/>
       <c r="D79" s="63" t="n">
@@ -10513,18 +10543,18 @@
       </c>
       <c r="F79" s="63"/>
       <c r="G79" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H79" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="63" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B80" s="63" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C80" s="63"/>
       <c r="D80" s="63" t="n">
@@ -10535,18 +10565,18 @@
       </c>
       <c r="F80" s="63"/>
       <c r="G80" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H80" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="81" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B81" s="63" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C81" s="63"/>
       <c r="D81" s="63" t="n">
@@ -10557,18 +10587,18 @@
       </c>
       <c r="F81" s="63"/>
       <c r="G81" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H81" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="81" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B82" s="63" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C82" s="63"/>
       <c r="D82" s="63" t="n">
@@ -10579,18 +10609,18 @@
       </c>
       <c r="F82" s="63"/>
       <c r="G82" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H82" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="81" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C83" s="63"/>
       <c r="D83" s="63" t="n">
@@ -10600,21 +10630,21 @@
         <v>-18258.52</v>
       </c>
       <c r="F83" s="63" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G83" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H83" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="81" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B84" s="63" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C84" s="63"/>
       <c r="D84" s="63" t="n">
@@ -10625,18 +10655,18 @@
       </c>
       <c r="F84" s="63"/>
       <c r="G84" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H84" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="81" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B85" s="63" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C85" s="63"/>
       <c r="D85" s="63" t="n">
@@ -10646,21 +10676,21 @@
         <v>-90253.52</v>
       </c>
       <c r="F85" s="63" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G85" s="80" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H85" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="81" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B86" s="63" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C86" s="63"/>
       <c r="D86" s="63" t="n">
@@ -10670,21 +10700,21 @@
         <v>-98421.52</v>
       </c>
       <c r="F86" s="63" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G86" s="80" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H86" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="86" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B87" s="67" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C87" s="67" t="n">
         <v>50000</v>
@@ -10694,19 +10724,19 @@
         <v>-48421.52</v>
       </c>
       <c r="F87" s="67" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G87" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H87" s="67"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="86" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B88" s="67" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C88" s="67" t="n">
         <v>30000</v>
@@ -10716,10 +10746,10 @@
         <v>-18421.52</v>
       </c>
       <c r="F88" s="67" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G88" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H88" s="67"/>
     </row>
@@ -10728,7 +10758,7 @@
         <v>95</v>
       </c>
       <c r="B89" s="63" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C89" s="63"/>
       <c r="D89" s="63" t="n">
@@ -10738,13 +10768,13 @@
         <v>-18428.41</v>
       </c>
       <c r="F89" s="63" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G89" s="80" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H89" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10752,7 +10782,7 @@
         <v>95</v>
       </c>
       <c r="B90" s="67" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C90" s="67" t="n">
         <v>2077.7</v>
@@ -10762,10 +10792,10 @@
         <v>-16350.71</v>
       </c>
       <c r="F90" s="67" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G90" s="84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H90" s="67"/>
     </row>
@@ -10774,7 +10804,7 @@
         <v>40</v>
       </c>
       <c r="B91" s="63" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C91" s="63"/>
       <c r="D91" s="63" t="n">
@@ -10785,15 +10815,15 @@
       </c>
       <c r="F91" s="63"/>
       <c r="G91" s="80" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H91" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E92" s="87" t="n">
         <v>-21406.71</v>
@@ -10801,13 +10831,13 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="88" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B95" s="89"/>
       <c r="C95" s="89"/>
@@ -10815,7 +10845,7 @@
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="89" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B96" s="89"/>
       <c r="C96" s="89"/>
@@ -10825,7 +10855,7 @@
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="89" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B97" s="89"/>
       <c r="C97" s="89"/>
@@ -11774,7 +11804,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11785,7 +11815,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -11802,33 +11832,33 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H4" s="61" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C5" s="53"/>
       <c r="D5" s="54" t="n">
@@ -11839,21 +11869,21 @@
         <v>-30615.71</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G5" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H5" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="53"/>
       <c r="D6" s="54" t="n">
@@ -11864,21 +11894,21 @@
         <v>-30726.26</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="54" t="n">
@@ -11889,21 +11919,21 @@
         <v>-32950.75</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="54" t="n">
@@ -11914,21 +11944,21 @@
         <v>-36906.75</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H8" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="54" t="n">
@@ -11939,21 +11969,21 @@
         <v>-37098.25</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H9" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C10" s="53"/>
       <c r="D10" s="54" t="n">
@@ -11964,21 +11994,21 @@
         <v>-42807.34</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H10" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>16000</v>
@@ -11989,19 +12019,19 @@
         <v>-26807.34</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H11" s="67"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>40223</v>
@@ -12012,19 +12042,19 @@
         <v>13415.66</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H12" s="67"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>25772</v>
@@ -12035,19 +12065,19 @@
         <v>39187.66</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H13" s="67"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>41069</v>
@@ -12058,19 +12088,19 @@
         <v>80256.66</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H14" s="67"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>64849.85</v>
@@ -12081,19 +12111,19 @@
         <v>145106.51</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H15" s="67"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="54" t="n">
@@ -12104,21 +12134,21 @@
         <v>142606.51</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H16" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C17" s="53"/>
       <c r="D17" s="54" t="n">
@@ -12129,21 +12159,21 @@
         <v>124316.51</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H17" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="73" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="48" t="n">
@@ -12154,21 +12184,21 @@
         <v>86774.81</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="73" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="48" t="n">
@@ -12179,21 +12209,21 @@
         <v>85299.81</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C20" s="53"/>
       <c r="D20" s="54" t="n">
@@ -12204,13 +12234,13 @@
         <v>85253.91</v>
       </c>
       <c r="F20" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G20" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12218,7 +12248,7 @@
         <v>74</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>1298</v>
@@ -12230,7 +12260,7 @@
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H21" s="67"/>
     </row>
@@ -12239,7 +12269,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="54" t="n">
@@ -12250,21 +12280,21 @@
         <v>84051.91</v>
       </c>
       <c r="F22" s="56" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>55238</v>
@@ -12275,19 +12305,19 @@
         <v>139289.91</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H23" s="67"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="73" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="48" t="n">
@@ -12298,21 +12328,21 @@
         <v>119589.91</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="73" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="48" t="n">
@@ -12323,21 +12353,21 @@
         <v>118409.91</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G25" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>96620</v>
@@ -12349,16 +12379,16 @@
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H26" s="67"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>5036</v>
@@ -12370,16 +12400,16 @@
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H27" s="67"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>23069</v>
@@ -12391,16 +12421,16 @@
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H28" s="67"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>18990</v>
@@ -12411,19 +12441,19 @@
         <v>262124.91</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H29" s="67"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>82721.75</v>
@@ -12434,19 +12464,19 @@
         <v>344846.66</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H30" s="67"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="73" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C31" s="47"/>
       <c r="D31" s="48" t="n">
@@ -12457,21 +12487,21 @@
         <v>175001.36</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H31" s="63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>5000</v>
@@ -12482,19 +12512,19 @@
         <v>180001.36</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H32" s="67"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="73" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C33" s="47"/>
       <c r="D33" s="48" t="n">
@@ -12505,21 +12535,21 @@
         <v>104936.36</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G33" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H33" s="63" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>129446</v>
@@ -12530,19 +12560,19 @@
         <v>234382.36</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H34" s="67"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="59" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C35" s="53"/>
       <c r="D35" s="54" t="n">
@@ -12553,21 +12583,21 @@
         <v>221747.36</v>
       </c>
       <c r="F35" s="56" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H35" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="54" t="n">
@@ -12578,21 +12608,21 @@
         <v>209992.36</v>
       </c>
       <c r="F36" s="56" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G36" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="59" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C37" s="53"/>
       <c r="D37" s="54" t="n">
@@ -12603,21 +12633,21 @@
         <v>197478.36</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H37" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>29500</v>
@@ -12628,19 +12658,19 @@
         <v>226978.36</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H38" s="67"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>15340</v>
@@ -12651,19 +12681,19 @@
         <v>242318.36</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H39" s="67"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>12675</v>
@@ -12674,19 +12704,19 @@
         <v>254993.36</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H40" s="67"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="59" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B41" s="52" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C41" s="53"/>
       <c r="D41" s="54" t="n">
@@ -12697,21 +12727,21 @@
         <v>248064.6</v>
       </c>
       <c r="F41" s="56" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H41" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>142805.25</v>
@@ -12722,19 +12752,19 @@
         <v>390869.85</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H42" s="67"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="73" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C43" s="47"/>
       <c r="D43" s="48" t="n">
@@ -12745,10 +12775,10 @@
         <v>385869.85</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G43" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H43" s="63"/>
     </row>
@@ -12757,7 +12787,7 @@
         <v>111</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C44" s="47"/>
       <c r="D44" s="48" t="n">
@@ -12768,10 +12798,10 @@
         <v>340267.36</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H44" s="63"/>
     </row>
@@ -12780,7 +12810,7 @@
         <v>111</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>45599.41</v>
@@ -12791,10 +12821,10 @@
         <v>385866.77</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H45" s="67"/>
     </row>
@@ -12803,7 +12833,7 @@
         <v>111</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>3.08</v>
@@ -12815,7 +12845,7 @@
       </c>
       <c r="F46" s="11"/>
       <c r="G46" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H46" s="67"/>
     </row>
@@ -12824,7 +12854,7 @@
         <v>111</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>286847</v>
@@ -12835,10 +12865,10 @@
         <v>672716.85</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H47" s="67"/>
     </row>
@@ -12847,7 +12877,7 @@
         <v>111</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C48" s="47"/>
       <c r="D48" s="48" t="n">
@@ -12858,10 +12888,10 @@
         <v>656466.85</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G48" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H48" s="63"/>
     </row>
@@ -12870,7 +12900,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>42772</v>
@@ -12882,16 +12912,16 @@
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H49" s="67"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B50" s="52" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C50" s="53"/>
       <c r="D50" s="54" t="n">
@@ -12902,21 +12932,21 @@
         <v>699067.85</v>
       </c>
       <c r="F50" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G50" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B51" s="52" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C51" s="53"/>
       <c r="D51" s="54" t="n">
@@ -12927,21 +12957,21 @@
         <v>686140.87</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H51" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C52" s="53"/>
       <c r="D52" s="54" t="n">
@@ -12952,21 +12982,21 @@
         <v>676540.87</v>
       </c>
       <c r="F52" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G52" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H52" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="54" t="n">
@@ -12977,21 +13007,21 @@
         <v>672540.87</v>
       </c>
       <c r="F53" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H53" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C54" s="53"/>
       <c r="D54" s="54" t="n">
@@ -13002,21 +13032,21 @@
         <v>665540.87</v>
       </c>
       <c r="F54" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G54" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H54" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B55" s="52" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C55" s="53"/>
       <c r="D55" s="54" t="n">
@@ -13027,21 +13057,21 @@
         <v>662540.87</v>
       </c>
       <c r="F55" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H55" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B56" s="52" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C56" s="53"/>
       <c r="D56" s="54" t="n">
@@ -13052,21 +13082,21 @@
         <v>657840.87</v>
       </c>
       <c r="F56" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G56" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H56" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B57" s="52" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C57" s="53"/>
       <c r="D57" s="54" t="n">
@@ -13077,21 +13107,21 @@
         <v>648990.87</v>
       </c>
       <c r="F57" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H57" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B58" s="52" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C58" s="53"/>
       <c r="D58" s="54" t="n">
@@ -13102,21 +13132,21 @@
         <v>636010.87</v>
       </c>
       <c r="F58" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G58" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H58" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B59" s="52" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C59" s="53"/>
       <c r="D59" s="54" t="n">
@@ -13127,21 +13157,21 @@
         <v>625228.23</v>
       </c>
       <c r="F59" s="56" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H59" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B60" s="52" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C60" s="53"/>
       <c r="D60" s="54" t="n">
@@ -13152,21 +13182,21 @@
         <v>621688.23</v>
       </c>
       <c r="F60" s="56" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G60" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H60" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="59" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B61" s="52" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C61" s="53" t="n">
         <v>4839</v>
@@ -13177,19 +13207,19 @@
         <v>626527.23</v>
       </c>
       <c r="F61" s="56" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H61" s="65"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B62" s="52" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C62" s="53"/>
       <c r="D62" s="54" t="n">
@@ -13200,21 +13230,21 @@
         <v>606757.23</v>
       </c>
       <c r="F62" s="56" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G62" s="51" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H62" s="65" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="59" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B63" s="52" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C63" s="53" t="n">
         <v>30000</v>
@@ -13225,19 +13255,19 @@
         <v>636757.23</v>
       </c>
       <c r="F63" s="56" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G63" s="51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H63" s="65"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C64" s="53"/>
       <c r="D64" s="54" t="n">
@@ -13248,21 +13278,21 @@
         <v>635400.23</v>
       </c>
       <c r="F64" s="56" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="G64" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H64" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="59" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B65" s="52" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C65" s="53"/>
       <c r="D65" s="54" t="n">
@@ -13274,16 +13304,16 @@
       </c>
       <c r="F65" s="56"/>
       <c r="G65" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H65" s="65"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B66" s="52" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C66" s="53"/>
       <c r="D66" s="54" t="n">
@@ -13294,21 +13324,21 @@
         <v>601860.23</v>
       </c>
       <c r="F66" s="56" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G66" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H66" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B67" s="52" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C67" s="53"/>
       <c r="D67" s="54" t="n">
@@ -13319,21 +13349,21 @@
         <v>597666.59</v>
       </c>
       <c r="F67" s="56" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G67" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H67" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B68" s="52" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C68" s="53"/>
       <c r="D68" s="54" t="n">
@@ -13344,21 +13374,21 @@
         <v>505168.19</v>
       </c>
       <c r="F68" s="56" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H68" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B69" s="52" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C69" s="53"/>
       <c r="D69" s="54" t="n">
@@ -13369,21 +13399,21 @@
         <v>503343.19</v>
       </c>
       <c r="F69" s="56" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G69" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H69" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B70" s="52" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C70" s="53"/>
       <c r="D70" s="54" t="n">
@@ -13394,21 +13424,21 @@
         <v>467584.38</v>
       </c>
       <c r="F70" s="56" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G70" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H70" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B71" s="52" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C71" s="53"/>
       <c r="D71" s="54" t="n">
@@ -13419,21 +13449,21 @@
         <v>276725.87</v>
       </c>
       <c r="F71" s="56" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G71" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H71" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C72" s="53"/>
       <c r="D72" s="54" t="n">
@@ -13444,21 +13474,21 @@
         <v>272640.87</v>
       </c>
       <c r="F72" s="56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G72" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H72" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="59" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B73" s="52" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C73" s="53"/>
       <c r="D73" s="54" t="n">
@@ -13469,21 +13499,21 @@
         <v>246675.87</v>
       </c>
       <c r="F73" s="56" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G73" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H73" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B74" s="52" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C74" s="53"/>
       <c r="D74" s="54" t="n">
@@ -13494,19 +13524,19 @@
         <v>245415.87</v>
       </c>
       <c r="F74" s="56" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="G74" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H74" s="65"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C75" s="53"/>
       <c r="D75" s="54" t="n">
@@ -13517,19 +13547,19 @@
         <v>242835.87</v>
       </c>
       <c r="F75" s="56" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="G75" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H75" s="65"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C76" s="53"/>
       <c r="D76" s="54" t="n">
@@ -13540,21 +13570,21 @@
         <v>237779.87</v>
       </c>
       <c r="F76" s="56" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G76" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H76" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B77" s="52" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C77" s="53" t="n">
         <v>47973.78</v>
@@ -13565,19 +13595,19 @@
         <v>285753.65</v>
       </c>
       <c r="F77" s="56" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G77" s="51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H77" s="65"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C78" s="53"/>
       <c r="D78" s="54" t="n">
@@ -13588,21 +13618,21 @@
         <v>160753.65</v>
       </c>
       <c r="F78" s="56" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G78" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H78" s="65" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="59" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B79" s="52" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C79" s="53"/>
       <c r="D79" s="54" t="n">
@@ -13613,21 +13643,21 @@
         <v>92809.65</v>
       </c>
       <c r="F79" s="56" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G79" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H79" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="59" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C80" s="53" t="n">
         <v>25000</v>
@@ -13638,19 +13668,19 @@
         <v>117809.65</v>
       </c>
       <c r="F80" s="56" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="G80" s="51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H80" s="65"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="59" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C81" s="53"/>
       <c r="D81" s="54" t="n">
@@ -13661,21 +13691,21 @@
         <v>117804.15</v>
       </c>
       <c r="F81" s="56" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G81" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H81" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="59" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B82" s="52" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C82" s="53"/>
       <c r="D82" s="54" t="n">
@@ -13686,18 +13716,18 @@
         <v>117658.66</v>
       </c>
       <c r="F82" s="56" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G82" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H82" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C83" s="91"/>
       <c r="D83" s="91"/>
@@ -13708,7 +13738,7 @@
     </row>
     <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="93" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B84" s="93"/>
       <c r="C84" s="93"/>
@@ -13725,7 +13755,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="94" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B86" s="94"/>
       <c r="C86" s="94"/>
@@ -13737,7 +13767,7 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="95" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B87" s="95"/>
       <c r="C87" s="96"/>
@@ -13749,7 +13779,7 @@
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="95" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B88" s="95"/>
       <c r="C88" s="96"/>
@@ -13761,7 +13791,7 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="95" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B89" s="95"/>
       <c r="C89" s="96"/>
@@ -14766,7 +14796,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14777,7 +14807,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -14795,33 +14825,33 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E4" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H4" s="61" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="59" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C5" s="53"/>
       <c r="D5" s="54" t="n">
@@ -14832,21 +14862,21 @@
         <v>117568.66</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G5" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H5" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="59" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C6" s="53"/>
       <c r="D6" s="54" t="n">
@@ -14857,21 +14887,21 @@
         <v>108419.66</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="54" t="n">
@@ -14882,21 +14912,21 @@
         <v>108319.01</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H7" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="54" t="n">
@@ -14907,21 +14937,21 @@
         <v>108308.01</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H8" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="54" t="n">
@@ -14932,21 +14962,21 @@
         <v>105153.82</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H9" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C10" s="53"/>
       <c r="D10" s="54" t="n">
@@ -14957,21 +14987,21 @@
         <v>101197.82</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H10" s="65" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="57" t="n">
@@ -14982,21 +15012,21 @@
         <v>101006.32</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H11" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="57" t="n">
@@ -15007,21 +15037,21 @@
         <v>97977.92</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H12" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="57" t="n">
@@ -15032,13 +15062,13 @@
         <v>91188.92</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H13" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15046,7 +15076,7 @@
         <v>46300</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="57" t="n">
@@ -15057,13 +15087,13 @@
         <v>90735.92</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H14" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15071,7 +15101,7 @@
         <v>46300</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="57" t="n">
@@ -15082,13 +15112,13 @@
         <v>84266.92</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H15" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15096,7 +15126,7 @@
         <v>46300</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>83515</v>
@@ -15107,10 +15137,10 @@
         <v>167781.92</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H16" s="67"/>
     </row>
@@ -15119,7 +15149,7 @@
         <v>46300</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>25772</v>
@@ -15130,10 +15160,10 @@
         <v>193553.92</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H17" s="67"/>
     </row>
@@ -15142,7 +15172,7 @@
         <v>46300</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="57" t="n">
@@ -15153,13 +15183,13 @@
         <v>123851.91</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H18" s="67" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15167,7 +15197,7 @@
         <v>46300</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="57" t="n">
@@ -15178,13 +15208,13 @@
         <v>104931.91</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H19" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15192,7 +15222,7 @@
         <v>46301</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>34618</v>
@@ -15203,10 +15233,10 @@
         <v>139549.91</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H20" s="67"/>
     </row>
@@ -15215,7 +15245,7 @@
         <v>46301</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="57" t="n">
@@ -15226,13 +15256,13 @@
         <v>139495.01</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H21" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15240,7 +15270,7 @@
         <v>46301</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>80000</v>
@@ -15251,10 +15281,10 @@
         <v>219495.01</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H22" s="67"/>
     </row>
@@ -15263,7 +15293,7 @@
         <v>46301</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>13541</v>
@@ -15274,10 +15304,10 @@
         <v>233036.01</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H23" s="67"/>
     </row>
@@ -15286,7 +15316,7 @@
         <v>46301</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="57" t="n">
@@ -15297,13 +15327,13 @@
         <v>220350.3</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H24" s="67" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15311,7 +15341,7 @@
         <v>46302</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>5063</v>
@@ -15322,10 +15352,10 @@
         <v>225413.3</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H25" s="67"/>
     </row>
@@ -15334,7 +15364,7 @@
         <v>46302</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="57" t="n">
@@ -15345,13 +15375,13 @@
         <v>-4586.69999999995</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H26" s="67" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15359,7 +15389,7 @@
         <v>46303</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>20000</v>
@@ -15370,10 +15400,10 @@
         <v>15413.3</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H27" s="67"/>
     </row>
@@ -15382,7 +15412,7 @@
         <v>46303</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>77278</v>
@@ -15393,10 +15423,10 @@
         <v>92691.3000000001</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H28" s="67"/>
     </row>
@@ -15405,7 +15435,7 @@
         <v>46303</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="57" t="n">
@@ -15416,13 +15446,13 @@
         <v>87381.3000000001</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H29" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15430,7 +15460,7 @@
         <v>46304</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>16400</v>
@@ -15441,10 +15471,10 @@
         <v>103781.3</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H30" s="67"/>
     </row>
@@ -15453,7 +15483,7 @@
         <v>46306</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="57" t="n">
@@ -15464,13 +15494,13 @@
         <v>96806.45</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H31" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15478,7 +15508,7 @@
         <v>46306</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>13570</v>
@@ -15489,10 +15519,10 @@
         <v>110376.45</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H32" s="67"/>
     </row>
@@ -15501,7 +15531,7 @@
         <v>46306</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>15340</v>
@@ -15512,10 +15542,10 @@
         <v>125716.45</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H33" s="67"/>
     </row>
@@ -15524,7 +15554,7 @@
         <v>46306</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>29500</v>
@@ -15535,10 +15565,10 @@
         <v>155216.45</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H34" s="67"/>
     </row>
@@ -15547,7 +15577,7 @@
         <v>46306</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="57" t="n">
@@ -15558,13 +15588,13 @@
         <v>135216.45</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H35" s="67" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15572,7 +15602,7 @@
         <v>46306</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="57" t="n">
@@ -15583,13 +15613,13 @@
         <v>124402.45</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H36" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15597,7 +15627,7 @@
         <v>46306</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="57" t="n">
@@ -15608,13 +15638,13 @@
         <v>121184.45</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H37" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15622,7 +15652,7 @@
         <v>46306</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="57" t="n">
@@ -15633,13 +15663,13 @@
         <v>110701.45</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H38" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15647,7 +15677,7 @@
         <v>46306</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="57" t="n">
@@ -15658,13 +15688,13 @@
         <v>90701.45</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H39" s="67" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15672,7 +15702,7 @@
         <v>46307</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="57" t="n">
@@ -15683,13 +15713,13 @@
         <v>81851.45</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H40" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15697,7 +15727,7 @@
         <v>46307</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="57" t="n">
@@ -15708,13 +15738,13 @@
         <v>68871.45</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H41" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15722,7 +15752,7 @@
         <v>46307</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>15741</v>
@@ -15733,10 +15763,10 @@
         <v>84612.45</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H42" s="67"/>
     </row>
@@ -15745,7 +15775,7 @@
         <v>46307</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>20000</v>
@@ -15756,10 +15786,10 @@
         <v>104612.45</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H43" s="67"/>
     </row>
@@ -15768,7 +15798,7 @@
         <v>46308</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>156403</v>
@@ -15779,10 +15809,10 @@
         <v>261015.45</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H44" s="67"/>
     </row>
@@ -15791,7 +15821,7 @@
         <v>46308</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="57" t="n">
@@ -15802,13 +15832,13 @@
         <v>244495.45</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H45" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15816,7 +15846,7 @@
         <v>46308</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>6513</v>
@@ -15827,10 +15857,10 @@
         <v>251008.45</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H46" s="67"/>
     </row>
@@ -15839,7 +15869,7 @@
         <v>46309</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="57" t="n">
@@ -15850,10 +15880,10 @@
         <v>205403.07</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H47" s="67"/>
     </row>
@@ -15862,7 +15892,7 @@
         <v>46309</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>45602.49</v>
@@ -15873,10 +15903,10 @@
         <v>251005.56</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H48" s="67"/>
     </row>
@@ -15885,7 +15915,7 @@
         <v>46309</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>2.89</v>
@@ -15897,7 +15927,7 @@
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H49" s="67"/>
     </row>
@@ -15906,7 +15936,7 @@
         <v>46309</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="57" t="n">
@@ -15917,19 +15947,21 @@
         <v>220361.45</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H50" s="67"/>
+        <v>131</v>
+      </c>
+      <c r="H50" s="67" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="n">
         <v>46309</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="57" t="n">
@@ -15940,13 +15972,13 @@
         <v>200591.45</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H51" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15954,7 +15986,7 @@
         <v>46309</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="57" t="n">
@@ -15965,13 +15997,13 @@
         <v>196913.45</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H52" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15979,7 +16011,7 @@
         <v>46309</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="57" t="n">
@@ -15990,13 +16022,13 @@
         <v>192213.45</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H53" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16004,7 +16036,7 @@
         <v>46309</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="57" t="n">
@@ -16015,13 +16047,13 @@
         <v>188213.45</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H54" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16029,7 +16061,7 @@
         <v>46309</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="57" t="n">
@@ -16040,13 +16072,13 @@
         <v>178613.45</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H55" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16054,7 +16086,7 @@
         <v>46309</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="57" t="n">
@@ -16065,13 +16097,13 @@
         <v>171613.45</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H56" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16079,7 +16111,7 @@
         <v>46309</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="57" t="n">
@@ -16090,13 +16122,13 @@
         <v>168613.45</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H57" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16104,7 +16136,7 @@
         <v>46309</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="57" t="n">
@@ -16115,13 +16147,13 @@
         <v>166195.45</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H58" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16129,7 +16161,7 @@
         <v>46309</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="57" t="n">
@@ -16140,10 +16172,10 @@
         <v>165795.45</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H59" s="67"/>
     </row>
@@ -16152,7 +16184,7 @@
         <v>46310</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="57" t="n">
@@ -16163,13 +16195,13 @@
         <v>160083.27</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H60" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16177,7 +16209,7 @@
         <v>46310</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="57" t="n">
@@ -16188,18 +16220,18 @@
         <v>159912.27</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H61" s="67" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C62" s="91"/>
       <c r="D62" s="91"/>
@@ -16210,7 +16242,7 @@
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="93" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B63" s="93"/>
       <c r="C63" s="93"/>
@@ -16223,7 +16255,7 @@
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="94" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B65" s="94"/>
       <c r="C65" s="94"/>
@@ -16235,7 +16267,7 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="95" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B66" s="95"/>
       <c r="C66" s="96"/>
@@ -16247,19 +16279,19 @@
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="95" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B67" s="95"/>
       <c r="C67" s="96"/>
       <c r="D67" s="90" t="n">
         <f aca="false">SUMIF(H5:H61,"לא",D5:D61)</f>
-        <v>352387.72</v>
+        <v>383034.72</v>
       </c>
       <c r="E67" s="91"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="95" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B68" s="95"/>
       <c r="C68" s="96"/>
@@ -16272,7 +16304,7 @@
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="94" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B70" s="94"/>
       <c r="C70" s="94"/>
@@ -16287,25 +16319,25 @@
         <v>5</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E71" s="97" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H71" s="61" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16313,7 +16345,7 @@
         <v>46315</v>
       </c>
       <c r="B72" s="99" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C72" s="100"/>
       <c r="D72" s="101" t="n">
@@ -16324,13 +16356,13 @@
         <v>155867.69</v>
       </c>
       <c r="F72" s="103" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="G72" s="104" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H72" s="105" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16338,7 +16370,7 @@
         <v>46315</v>
       </c>
       <c r="B73" s="99" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C73" s="100"/>
       <c r="D73" s="101" t="n">
@@ -16349,13 +16381,13 @@
         <v>154042.69</v>
       </c>
       <c r="F73" s="103" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G73" s="104" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H73" s="105" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16363,7 +16395,7 @@
         <v>46315</v>
       </c>
       <c r="B74" s="99" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C74" s="100"/>
       <c r="D74" s="101" t="n">
@@ -16374,13 +16406,13 @@
         <v>118610.12</v>
       </c>
       <c r="F74" s="103" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G74" s="104" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H74" s="105" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16388,7 +16420,7 @@
         <v>46320</v>
       </c>
       <c r="B75" s="99" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C75" s="100"/>
       <c r="D75" s="101" t="n">
@@ -16399,13 +16431,13 @@
         <v>100347.22</v>
       </c>
       <c r="F75" s="103" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="G75" s="104" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H75" s="105" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16413,7 +16445,7 @@
         <v>46320</v>
       </c>
       <c r="B76" s="99" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C76" s="100"/>
       <c r="D76" s="101" t="n">
@@ -16424,13 +16456,13 @@
         <v>55776.2200000001</v>
       </c>
       <c r="F76" s="103" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="G76" s="104" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H76" s="105" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16438,7 +16470,7 @@
         <v>46320</v>
       </c>
       <c r="B77" s="99" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C77" s="100"/>
       <c r="D77" s="101" t="n">
@@ -16449,18 +16481,18 @@
         <v>-69223.7799999999</v>
       </c>
       <c r="F77" s="103" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="G77" s="104" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H77" s="105" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C78" s="91"/>
       <c r="D78" s="91"/>
@@ -17441,7 +17473,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17451,7 +17483,7 @@
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
@@ -17460,24 +17492,24 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="106" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B5" s="107" t="s">
         <v>30</v>
@@ -17489,12 +17521,12 @@
         <v>125000</v>
       </c>
       <c r="E5" s="109" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="106" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B6" s="107" t="s">
         <v>38</v>
@@ -17506,12 +17538,12 @@
         <v>208316.3</v>
       </c>
       <c r="E6" s="109" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="106" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B7" s="107" t="s">
         <v>42</v>
@@ -17523,12 +17555,12 @@
         <v>18262.9</v>
       </c>
       <c r="E7" s="109" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="106" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B8" s="107" t="s">
         <v>42</v>
@@ -17540,12 +17572,12 @@
         <v>44571</v>
       </c>
       <c r="E8" s="109" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="106" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B9" s="107" t="s">
         <v>42</v>
@@ -17557,12 +17589,12 @@
         <v>107834.3</v>
       </c>
       <c r="E9" s="109" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="106" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B10" s="107" t="s">
         <v>42</v>
@@ -17579,7 +17611,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="110" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B11" s="110"/>
       <c r="C11" s="110"/>
@@ -17591,7 +17623,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
@@ -17600,18 +17632,18 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="106" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B14" s="107"/>
       <c r="C14" s="107"/>
@@ -17629,13 +17661,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -17644,28 +17676,28 @@
         <v>38</v>
       </c>
       <c r="B18" s="106" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C18" s="108" t="n">
         <v>208316.3</v>
       </c>
       <c r="D18" s="113" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E18" s="114"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="107" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B19" s="106" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C19" s="108" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E19" s="114"/>
     </row>
@@ -17674,13 +17706,13 @@
         <v>42</v>
       </c>
       <c r="B20" s="106" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C20" s="108" t="n">
         <v>18262.9</v>
       </c>
       <c r="D20" s="113" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E20" s="114"/>
     </row>
@@ -17689,28 +17721,28 @@
         <v>42</v>
       </c>
       <c r="B21" s="106" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C21" s="108" t="n">
         <v>44571</v>
       </c>
       <c r="D21" s="113" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E21" s="114"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="107" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B22" s="106" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C22" s="108" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="113" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E22" s="114"/>
     </row>
@@ -17719,13 +17751,13 @@
         <v>42</v>
       </c>
       <c r="B23" s="106" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C23" s="108" t="n">
         <v>107834.3</v>
       </c>
       <c r="D23" s="113" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E23" s="114"/>
     </row>
@@ -17734,34 +17766,34 @@
         <v>42</v>
       </c>
       <c r="B24" s="106" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C24" s="108" t="n">
         <v>35432.57</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E24" s="114"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="107" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B25" s="106" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C25" s="108" t="n">
         <v>12676.86</v>
       </c>
       <c r="D25" s="113" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E25" s="114"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="110" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B26" s="110"/>
       <c r="C26" s="21" t="n">
@@ -17774,7 +17806,7 @@
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="39" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B28" s="39"/>
       <c r="C28" s="39"/>
@@ -17795,7 +17827,7 @@
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="88" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B32" s="89"/>
       <c r="C32" s="89"/>
@@ -17803,70 +17835,70 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="115" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C33" s="115" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D33" s="116" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E33" s="117"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="118" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B34" s="118" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C34" s="119" t="n">
         <v>15803.8</v>
       </c>
       <c r="D34" s="120" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E34" s="117"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="118" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B35" s="118" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C35" s="119" t="n">
         <v>2367</v>
       </c>
       <c r="D35" s="120" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E35" s="117"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="118" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B36" s="118" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C36" s="119" t="n">
         <v>8425</v>
       </c>
       <c r="D36" s="120" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E36" s="117"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="118" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B37" s="118" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C37" s="119" t="n">
         <v>91496</v>
@@ -17876,157 +17908,157 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="118" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B38" s="118" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C38" s="119" t="n">
         <v>112041</v>
       </c>
       <c r="D38" s="120" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E38" s="117"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="118" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B39" s="118" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C39" s="119" t="n">
         <v>120397</v>
       </c>
       <c r="D39" s="120" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E39" s="117"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="118" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B40" s="118" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C40" s="119" t="n">
         <v>163</v>
       </c>
       <c r="D40" s="120" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E40" s="117"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="118" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B41" s="118" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C41" s="119" t="n">
         <v>55833</v>
       </c>
       <c r="D41" s="120" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E41" s="117"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="118" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B42" s="118" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C42" s="119" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="120" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E42" s="117"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="118" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B43" s="118" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C43" s="119" t="n">
         <v>66573</v>
       </c>
       <c r="D43" s="120" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E43" s="117"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="118" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B44" s="118" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C44" s="119" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="120" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E44" s="117"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="118" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B45" s="118" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C45" s="119" t="n">
         <v>7723</v>
       </c>
       <c r="D45" s="120" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E45" s="117"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="118" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B46" s="118" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C46" s="119" t="n">
         <v>19171</v>
       </c>
       <c r="D46" s="120" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E46" s="117"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="118" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B47" s="118" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C47" s="119" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="120" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E47" s="117"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="121" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B48" s="122"/>
       <c r="C48" s="123" t="n">
@@ -18039,7 +18071,7 @@
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="88" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B50" s="88"/>
       <c r="C50" s="88"/>
@@ -18047,7 +18079,7 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C51" s="91" t="n">
         <v>159912.27</v>
@@ -18055,7 +18087,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C52" s="91" t="n">
         <f aca="false">C48</f>
@@ -18064,7 +18096,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="125" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B53" s="125"/>
       <c r="C53" s="126" t="n">
@@ -18075,7 +18107,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C54" s="91" t="n">
         <f aca="false">D28</f>
@@ -18084,7 +18116,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="127" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B55" s="127"/>
       <c r="C55" s="128" t="n">
@@ -18096,7 +18128,7 @@
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="88" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B57" s="88"/>
       <c r="C57" s="88"/>
@@ -18104,24 +18136,24 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="129" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B58" s="129" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C58" s="129" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D58" s="129" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="130" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B59" s="129" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C59" s="131" t="n">
         <v>2273</v>
@@ -18132,10 +18164,10 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="129" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B60" s="129" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C60" s="131" t="n">
         <v>1184</v>
@@ -18146,10 +18178,10 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="129" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B61" s="129" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C61" s="131" t="n">
         <v>2248</v>
@@ -18172,7 +18204,7 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="125" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B63" s="125"/>
       <c r="C63" s="126"/>
